--- a/utils/monday_sprint_sprint_2025-14.xlsx
+++ b/utils/monday_sprint_sprint_2025-14.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1314" uniqueCount="255">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1314" uniqueCount="256">
   <si>
     <t>Ticket</t>
   </si>
@@ -153,7 +153,7 @@
     <t>30/05/2025</t>
   </si>
   <si>
-    <t>14/03/2026</t>
+    <t>09/03/2026</t>
   </si>
   <si>
     <t>Maio</t>
@@ -429,7 +429,7 @@
     <t>25/04/2023</t>
   </si>
   <si>
-    <t>23/02/2026</t>
+    <t>18/02/2026</t>
   </si>
   <si>
     <t>Abril</t>
@@ -514,6 +514,9 @@
   </si>
   <si>
     <t>10/02/2025</t>
+  </si>
+  <si>
+    <t>19/05/2026</t>
   </si>
   <si>
     <t>Fevereiro</t>
@@ -3794,7 +3797,7 @@
         <v>166</v>
       </c>
       <c r="K59" s="2" t="s">
-        <v>17</v>
+        <v>167</v>
       </c>
       <c r="L59" s="2" t="s">
         <v>20</v>
@@ -3803,7 +3806,7 @@
         <v>25</v>
       </c>
       <c r="N59" s="2" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="60" spans="1:14" x14ac:dyDescent="0.25">
@@ -3820,10 +3823,10 @@
         <v>17</v>
       </c>
       <c r="E60" s="2" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="F60" s="2" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="G60" s="2" t="s">
         <v>28</v>
@@ -3852,7 +3855,7 @@
     </row>
     <row r="61" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A61" s="2" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B61" s="2" t="s">
         <v>15</v>
@@ -3864,10 +3867,10 @@
         <v>17</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F61" s="2" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="G61" s="2" t="s">
         <v>28</v>
@@ -3908,10 +3911,10 @@
         <v>17</v>
       </c>
       <c r="E62" s="2" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="F62" s="2" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="G62" s="2" t="s">
         <v>28</v>
@@ -3940,7 +3943,7 @@
     </row>
     <row r="63" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A63" s="2" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B63" s="2" t="s">
         <v>15</v>
@@ -3952,10 +3955,10 @@
         <v>17</v>
       </c>
       <c r="E63" s="2" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="F63" s="2" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="G63" s="2" t="s">
         <v>28</v>
@@ -3984,7 +3987,7 @@
     </row>
     <row r="64" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A64" s="2" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B64" s="2" t="s">
         <v>15</v>
@@ -3996,10 +3999,10 @@
         <v>17</v>
       </c>
       <c r="E64" s="2" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F64" s="2" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="G64" s="2" t="s">
         <v>19</v>
@@ -4028,7 +4031,7 @@
     </row>
     <row r="65" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A65" s="2" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B65" s="2" t="s">
         <v>15</v>
@@ -4040,10 +4043,10 @@
         <v>17</v>
       </c>
       <c r="E65" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F65" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="G65" s="2" t="s">
         <v>28</v>
@@ -4072,7 +4075,7 @@
     </row>
     <row r="66" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A66" s="2" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B66" s="2" t="s">
         <v>15</v>
@@ -4084,10 +4087,10 @@
         <v>30</v>
       </c>
       <c r="E66" s="2" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="F66" s="2" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="G66" s="2" t="s">
         <v>28</v>
@@ -4099,7 +4102,7 @@
         <v>34</v>
       </c>
       <c r="J66" s="2" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="K66" s="2" t="s">
         <v>17</v>
@@ -4116,7 +4119,7 @@
     </row>
     <row r="67" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A67" s="2" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B67" s="2" t="s">
         <v>15</v>
@@ -4128,10 +4131,10 @@
         <v>30</v>
       </c>
       <c r="E67" s="2" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="F67" s="2" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="G67" s="2" t="s">
         <v>19</v>
@@ -4143,7 +4146,7 @@
         <v>60</v>
       </c>
       <c r="J67" s="2" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="K67" s="2" t="s">
         <v>17</v>
@@ -4155,7 +4158,7 @@
         <v>25</v>
       </c>
       <c r="N67" s="2" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="68" spans="1:14" x14ac:dyDescent="0.25">
@@ -4172,10 +4175,10 @@
         <v>17</v>
       </c>
       <c r="E68" s="2" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="F68" s="2" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="G68" s="2" t="s">
         <v>19</v>
@@ -4204,7 +4207,7 @@
     </row>
     <row r="69" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A69" s="2" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B69" s="2" t="s">
         <v>15</v>
@@ -4216,10 +4219,10 @@
         <v>17</v>
       </c>
       <c r="E69" s="2" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F69" s="2" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="G69" s="2" t="s">
         <v>28</v>
@@ -4248,7 +4251,7 @@
     </row>
     <row r="70" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A70" s="2" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B70" s="2" t="s">
         <v>15</v>
@@ -4260,10 +4263,10 @@
         <v>17</v>
       </c>
       <c r="E70" s="2" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F70" s="2" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="G70" s="2" t="s">
         <v>28</v>
@@ -4292,7 +4295,7 @@
     </row>
     <row r="71" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A71" s="2" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B71" s="2" t="s">
         <v>15</v>
@@ -4304,10 +4307,10 @@
         <v>17</v>
       </c>
       <c r="E71" s="2" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="F71" s="2" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="G71" s="2" t="s">
         <v>28</v>
@@ -4336,7 +4339,7 @@
     </row>
     <row r="72" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A72" s="2" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B72" s="2" t="s">
         <v>15</v>
@@ -4348,10 +4351,10 @@
         <v>17</v>
       </c>
       <c r="E72" s="2" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F72" s="2" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="G72" s="2" t="s">
         <v>19</v>
@@ -4380,7 +4383,7 @@
     </row>
     <row r="73" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A73" s="2" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B73" s="2" t="s">
         <v>15</v>
@@ -4392,10 +4395,10 @@
         <v>17</v>
       </c>
       <c r="E73" s="2" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="F73" s="2" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="G73" s="2" t="s">
         <v>28</v>
@@ -4424,7 +4427,7 @@
     </row>
     <row r="74" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A74" s="2" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B74" s="2" t="s">
         <v>15</v>
@@ -4436,10 +4439,10 @@
         <v>17</v>
       </c>
       <c r="E74" s="2" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F74" s="2" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="G74" s="2" t="s">
         <v>28</v>
@@ -4480,10 +4483,10 @@
         <v>17</v>
       </c>
       <c r="E75" s="2" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F75" s="2" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="G75" s="2" t="s">
         <v>19</v>
@@ -4524,10 +4527,10 @@
         <v>17</v>
       </c>
       <c r="E76" s="2" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="F76" s="2" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="G76" s="2" t="s">
         <v>28</v>
@@ -4568,7 +4571,7 @@
         <v>30</v>
       </c>
       <c r="E77" s="2" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="F77" s="2" t="s">
         <v>59</v>
@@ -4612,10 +4615,10 @@
         <v>17</v>
       </c>
       <c r="E78" s="2" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F78" s="2" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="G78" s="2" t="s">
         <v>19</v>
@@ -4644,7 +4647,7 @@
     </row>
     <row r="79" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A79" s="2" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B79" s="2" t="s">
         <v>15</v>
@@ -4656,10 +4659,10 @@
         <v>17</v>
       </c>
       <c r="E79" s="2" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="F79" s="2" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="G79" s="2" t="s">
         <v>28</v>
@@ -4688,7 +4691,7 @@
     </row>
     <row r="80" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A80" s="2" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B80" s="2" t="s">
         <v>15</v>
@@ -4700,10 +4703,10 @@
         <v>17</v>
       </c>
       <c r="E80" s="2" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F80" s="2" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="G80" s="2" t="s">
         <v>28</v>
@@ -4732,7 +4735,7 @@
     </row>
     <row r="81" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A81" s="2" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="B81" s="2" t="s">
         <v>15</v>
@@ -4744,10 +4747,10 @@
         <v>17</v>
       </c>
       <c r="E81" s="2" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="F81" s="2" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="G81" s="2" t="s">
         <v>28</v>
@@ -4776,7 +4779,7 @@
     </row>
     <row r="82" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A82" s="2" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="B82" s="2" t="s">
         <v>15</v>
@@ -4788,10 +4791,10 @@
         <v>17</v>
       </c>
       <c r="E82" s="2" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="F82" s="2" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="G82" s="2" t="s">
         <v>28</v>
@@ -4820,7 +4823,7 @@
     </row>
     <row r="83" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A83" s="2" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="B83" s="2" t="s">
         <v>15</v>
@@ -4832,10 +4835,10 @@
         <v>17</v>
       </c>
       <c r="E83" s="2" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F83" s="2" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="G83" s="2" t="s">
         <v>19</v>
@@ -4864,7 +4867,7 @@
     </row>
     <row r="84" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A84" s="2" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B84" s="2" t="s">
         <v>15</v>
@@ -4876,10 +4879,10 @@
         <v>17</v>
       </c>
       <c r="E84" s="2" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="F84" s="2" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="G84" s="2" t="s">
         <v>28</v>
@@ -4908,7 +4911,7 @@
     </row>
     <row r="85" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A85" s="2" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="B85" s="2" t="s">
         <v>15</v>
@@ -4920,10 +4923,10 @@
         <v>30</v>
       </c>
       <c r="E85" s="2" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="F85" s="2" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="G85" s="2" t="s">
         <v>28</v>
@@ -4938,7 +4941,7 @@
         <v>35</v>
       </c>
       <c r="K85" s="2" t="s">
-        <v>17</v>
+        <v>167</v>
       </c>
       <c r="L85" s="2" t="s">
         <v>118</v>
@@ -4952,7 +4955,7 @@
     </row>
     <row r="86" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A86" s="2" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="B86" s="2" t="s">
         <v>15</v>
@@ -4964,10 +4967,10 @@
         <v>17</v>
       </c>
       <c r="E86" s="2" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="F86" s="2" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="G86" s="2" t="s">
         <v>28</v>
@@ -4996,7 +4999,7 @@
     </row>
     <row r="87" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A87" s="2" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="B87" s="2" t="s">
         <v>15</v>
@@ -5008,10 +5011,10 @@
         <v>30</v>
       </c>
       <c r="E87" s="2" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="F87" s="2" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="G87" s="2" t="s">
         <v>28</v>
@@ -5023,10 +5026,10 @@
         <v>60</v>
       </c>
       <c r="J87" s="2" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="K87" s="2" t="s">
-        <v>17</v>
+        <v>167</v>
       </c>
       <c r="L87" s="2" t="s">
         <v>118</v>
@@ -5035,12 +5038,12 @@
         <v>21</v>
       </c>
       <c r="N87" s="2" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
     </row>
     <row r="88" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A88" s="2" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="B88" s="2" t="s">
         <v>15</v>
@@ -5052,10 +5055,10 @@
         <v>17</v>
       </c>
       <c r="E88" s="2" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="F88" s="2" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="G88" s="2" t="s">
         <v>28</v>
@@ -5095,23 +5098,23 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="B1" s="3"/>
       <c r="C1" s="3"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B2" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="D2" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="E2" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="F2"/>
       <c r="G2"/>
@@ -5119,16 +5122,16 @@
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
@@ -5147,7 +5150,7 @@
     </row>
     <row r="21" spans="10:10" x14ac:dyDescent="0.25">
       <c r="J21" s="6" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="22" spans="10:11" x14ac:dyDescent="0.25">
@@ -5160,7 +5163,7 @@
     </row>
     <row r="23" spans="10:11" x14ac:dyDescent="0.25">
       <c r="J23" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="K23">
         <v>0</v>
@@ -5168,7 +5171,7 @@
     </row>
     <row r="24" spans="10:11" x14ac:dyDescent="0.25">
       <c r="J24" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="K24">
         <v>0</v>
@@ -5199,12 +5202,12 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B2">
         <v>87</v>
@@ -5228,25 +5231,25 @@
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="G9" s="6" t="s">
         <v>6</v>
       </c>
       <c r="J9" s="6" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="M9" s="6" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="P9" s="6" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="Q9" s="6" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.25">
@@ -5263,13 +5266,13 @@
         <v>67</v>
       </c>
       <c r="G10" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="H10">
         <v>0</v>
       </c>
       <c r="J10" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="K10">
         <v>0</v>
@@ -5301,7 +5304,7 @@
         <v>17</v>
       </c>
       <c r="J11" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="K11">
         <v>87</v>
@@ -5316,7 +5319,7 @@
         <v>25</v>
       </c>
       <c r="Q11">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="12" spans="4:17" x14ac:dyDescent="0.25">
@@ -5342,7 +5345,7 @@
         <v>40</v>
       </c>
       <c r="Q12">
-        <v>4</v>
+        <v>12</v>
       </c>
     </row>
     <row r="13" spans="4:17" x14ac:dyDescent="0.25">
@@ -5353,7 +5356,7 @@
         <v>3</v>
       </c>
       <c r="G13" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="H13">
         <v>0</v>
@@ -5368,18 +5371,18 @@
         <v>62</v>
       </c>
       <c r="Q13">
-        <v>35</v>
+        <v>28</v>
       </c>
     </row>
     <row r="14" spans="7:17" x14ac:dyDescent="0.25">
       <c r="G14" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="H14">
         <v>0</v>
       </c>
       <c r="M14" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="N14">
         <v>0</v>
@@ -5401,7 +5404,7 @@
     </row>
     <row r="16" spans="13:14" x14ac:dyDescent="0.25">
       <c r="M16" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="N16">
         <v>0</v>
@@ -5409,7 +5412,7 @@
     </row>
     <row r="17" spans="13:14" x14ac:dyDescent="0.25">
       <c r="M17" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="N17">
         <v>0</v>
@@ -5417,7 +5420,7 @@
     </row>
     <row r="19" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D19" s="6" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
     </row>
     <row r="20" ht="18" customHeight="1" spans="4:7" x14ac:dyDescent="0.25">
@@ -5428,7 +5431,7 @@
         <v>1</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="G20" s="1" t="s">
         <v>4</v>
@@ -5442,7 +5445,7 @@
         <v>15</v>
       </c>
       <c r="F21" s="2">
-        <v>1020</v>
+        <v>1015</v>
       </c>
       <c r="G21" s="2" t="s">
         <v>134</v>
@@ -5456,7 +5459,7 @@
         <v>15</v>
       </c>
       <c r="F22" s="2">
-        <v>1020</v>
+        <v>1015</v>
       </c>
       <c r="G22" s="2" t="s">
         <v>140</v>
@@ -5470,7 +5473,7 @@
         <v>15</v>
       </c>
       <c r="F23" s="2">
-        <v>1020</v>
+        <v>1015</v>
       </c>
       <c r="G23" s="2" t="s">
         <v>141</v>
@@ -5484,7 +5487,7 @@
         <v>15</v>
       </c>
       <c r="F24" s="2">
-        <v>1020</v>
+        <v>1015</v>
       </c>
       <c r="G24" s="2" t="s">
         <v>142</v>
@@ -5498,7 +5501,7 @@
         <v>15</v>
       </c>
       <c r="F25" s="2">
-        <v>1020</v>
+        <v>1015</v>
       </c>
       <c r="G25" s="2" t="s">
         <v>143</v>
@@ -5512,7 +5515,7 @@
         <v>15</v>
       </c>
       <c r="F26" s="2">
-        <v>1020</v>
+        <v>1015</v>
       </c>
       <c r="G26" s="2" t="s">
         <v>144</v>
@@ -5526,7 +5529,7 @@
         <v>15</v>
       </c>
       <c r="F27" s="2">
-        <v>1020</v>
+        <v>1015</v>
       </c>
       <c r="G27" s="2" t="s">
         <v>145</v>
@@ -5540,7 +5543,7 @@
         <v>15</v>
       </c>
       <c r="F28" s="2">
-        <v>769</v>
+        <v>772</v>
       </c>
       <c r="G28" s="2" t="s">
         <v>58</v>
@@ -5554,24 +5557,24 @@
         <v>15</v>
       </c>
       <c r="F29" s="2">
-        <v>769</v>
+        <v>772</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="30" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D30" s="2" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>15</v>
       </c>
       <c r="F30" s="2">
-        <v>458</v>
+        <v>461</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
   </sheetData>

--- a/utils/monday_sprint_sprint_2025-14.xlsx
+++ b/utils/monday_sprint_sprint_2025-14.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1403" uniqueCount="259">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1404" uniqueCount="276">
   <si>
     <t>Ticket</t>
   </si>
@@ -42,7 +42,7 @@
     <t>Equipe TI</t>
   </si>
   <si>
-    <t>Entrada Sprint</t>
+    <t>Abertura</t>
   </si>
   <si>
     <t>Encerramento</t>
@@ -51,7 +51,7 @@
     <t>Status</t>
   </si>
   <si>
-    <t>SLA (15 dias)</t>
+    <t>Dentro da SLA</t>
   </si>
   <si>
     <t>Semana</t>
@@ -60,7 +60,7 @@
     <t>Mês</t>
   </si>
   <si>
-    <t>31747</t>
+    <t>9270659115</t>
   </si>
   <si>
     <t>Setor não informado</t>
@@ -87,7 +87,7 @@
     <t>30/05/2025</t>
   </si>
   <si>
-    <t>N/A</t>
+    <t>12/07/2025</t>
   </si>
   <si>
     <t>Feito</t>
@@ -102,7 +102,7 @@
     <t>Maio</t>
   </si>
   <si>
-    <t>32041</t>
+    <t>9374881896</t>
   </si>
   <si>
     <t>Custos de Armazenagem/MP</t>
@@ -111,19 +111,19 @@
     <t>13/06/2025</t>
   </si>
   <si>
+    <t>30/06/2025</t>
+  </si>
+  <si>
     <t>A fazer</t>
   </si>
   <si>
-    <t>Aberto</t>
-  </si>
-  <si>
     <t>Semana 2</t>
   </si>
   <si>
     <t>Junho</t>
   </si>
   <si>
-    <t>31789</t>
+    <t>9270557969</t>
   </si>
   <si>
     <t>Novo código de setor.</t>
@@ -132,9 +132,15 @@
     <t>Média</t>
   </si>
   <si>
+    <t>13/07/2025</t>
+  </si>
+  <si>
     <t>32141</t>
   </si>
   <si>
+    <t>Logística</t>
+  </si>
+  <si>
     <t>Solicitação de serviço</t>
   </si>
   <si>
@@ -153,7 +159,7 @@
     <t>02/06/2026</t>
   </si>
   <si>
-    <t>31410</t>
+    <t>9170606416</t>
   </si>
   <si>
     <t>OTF p/ Fundição de Peças p/ Destruição</t>
@@ -165,409 +171,445 @@
     <t>Semana 3</t>
   </si>
   <si>
-    <t>32022</t>
+    <t>9374909734</t>
   </si>
   <si>
     <t>Apontamento Células de rebarbação automatizadas (Dalca e Lianco)</t>
   </si>
   <si>
-    <t>Boa tarde! Abrindo chamado referente ao desenvolvimento do sistema de apontamentos via CLP das células de rebarbação automatizadas. Atenciosamente,</t>
-  </si>
-  <si>
-    <t>Leonardo Barbosa de Moraes</t>
+    <t>07/07/2025</t>
+  </si>
+  <si>
+    <t>9374522996</t>
+  </si>
+  <si>
+    <t>Extensão da visão do relatório de busca de sequencias para depósito</t>
+  </si>
+  <si>
+    <t>Homologação</t>
+  </si>
+  <si>
+    <t>9375140754</t>
+  </si>
+  <si>
+    <t>Apontamento Ajustagem</t>
+  </si>
+  <si>
+    <t>09/07/2025</t>
+  </si>
+  <si>
+    <t>9402975204</t>
+  </si>
+  <si>
+    <t>Códigos para Cadastro</t>
+  </si>
+  <si>
+    <t>18/06/2025</t>
+  </si>
+  <si>
+    <t>9374643964</t>
+  </si>
+  <si>
+    <t>Atualização sistema mapeamento</t>
+  </si>
+  <si>
+    <t>25310</t>
+  </si>
+  <si>
+    <t>Sistema de Controle de Orçamento de Entregas de Venda</t>
+  </si>
+  <si>
+    <t>Boa Tarde Segue anexo escopo para criação do sistema de controle de orçamentos de Entrega de venda, para comparação com o realizado e provisionamento de custo para a controladoria.</t>
+  </si>
+  <si>
+    <t>26/05/2025</t>
+  </si>
+  <si>
+    <t>Semana 4</t>
+  </si>
+  <si>
+    <t>9459275689</t>
+  </si>
+  <si>
+    <t>Dados retroativos Qlick Sense</t>
+  </si>
+  <si>
+    <t>26/06/2025</t>
+  </si>
+  <si>
+    <t>9171564491</t>
+  </si>
+  <si>
+    <t>Novo Sistema</t>
+  </si>
+  <si>
+    <t>Criar agendamento de remessa para industrialização - Reunião</t>
+  </si>
+  <si>
+    <t>10/07/2025</t>
+  </si>
+  <si>
+    <t>9471491258</t>
+  </si>
+  <si>
+    <t>Exclusão de Entrega de EPI</t>
+  </si>
+  <si>
+    <t>27/06/2025</t>
+  </si>
+  <si>
+    <t>9471595253</t>
+  </si>
+  <si>
+    <t>ESTORNO 88890</t>
+  </si>
+  <si>
+    <t>9471615904</t>
+  </si>
+  <si>
+    <t>Alteração na Aplicação - "Requisição"</t>
+  </si>
+  <si>
+    <t>9471640521</t>
+  </si>
+  <si>
+    <t>Horímetro - Apontamento eletrônico Manipuladores</t>
+  </si>
+  <si>
+    <t>9471693013</t>
+  </si>
+  <si>
+    <t>Adequação no SMI para uso do Preset (Acabamento)</t>
+  </si>
+  <si>
+    <t>9471701751</t>
+  </si>
+  <si>
+    <t>[COMPRAS] Criação campo Forma de Pagamento - na tela de Cadastro de Fornecedo</t>
+  </si>
+  <si>
+    <t>02/07/2025</t>
+  </si>
+  <si>
+    <t>9471712679</t>
+  </si>
+  <si>
+    <t>Alteração na emissão de notas de remessa</t>
+  </si>
+  <si>
+    <t>03/07/2025</t>
+  </si>
+  <si>
+    <t>9471727792</t>
+  </si>
+  <si>
+    <t>Tempos dos modelos UPR</t>
+  </si>
+  <si>
+    <t>9471744125</t>
+  </si>
+  <si>
+    <t>Correção</t>
+  </si>
+  <si>
+    <t>Validação Solda - QlikSense</t>
+  </si>
+  <si>
+    <t>01/07/2025</t>
+  </si>
+  <si>
+    <t>9471753409</t>
+  </si>
+  <si>
+    <t>Divergência no tempo padrão rateio - IROG Usinagem</t>
+  </si>
+  <si>
+    <t>9471763280</t>
+  </si>
+  <si>
+    <t>Desenvolvimento de BI de apontamento</t>
+  </si>
+  <si>
+    <t>06/07/2025</t>
+  </si>
+  <si>
+    <t>9471771271</t>
+  </si>
+  <si>
+    <t>Informações QlikSense para engenharia</t>
+  </si>
+  <si>
+    <t>9471785585</t>
+  </si>
+  <si>
+    <t>Apareça o contentor</t>
+  </si>
+  <si>
+    <t>9471806275</t>
+  </si>
+  <si>
+    <t>Tela de pedido de compra</t>
+  </si>
+  <si>
+    <t>9471814299</t>
+  </si>
+  <si>
+    <t>Sistema de inventario</t>
+  </si>
+  <si>
+    <t>9471829965</t>
+  </si>
+  <si>
+    <t>Consulta de Pedido de Compra Nimbi</t>
+  </si>
+  <si>
+    <t>9471841169</t>
+  </si>
+  <si>
+    <t>[NIMBI] INTEGRAÇÃO DE IMPOSTOS NOS PEDIDOS</t>
+  </si>
+  <si>
+    <t>9471856159</t>
+  </si>
+  <si>
+    <t>Solicitação de colunas informando horário/quantidades de peças</t>
+  </si>
+  <si>
+    <t>9471863886</t>
+  </si>
+  <si>
+    <t>Solicitação de criação de área para acompanhamento de pedidos</t>
+  </si>
+  <si>
+    <t>9471929901</t>
+  </si>
+  <si>
+    <t>Solicitação quantidade de peça a ser coleta nesta tela</t>
+  </si>
+  <si>
+    <t>9471948429</t>
+  </si>
+  <si>
+    <t>Desenvolvimento de gráfico - aplicação Refugo Qlik Sense</t>
+  </si>
+  <si>
+    <t>08/07/2025</t>
+  </si>
+  <si>
+    <t>9471958634</t>
+  </si>
+  <si>
+    <t>Alteração aplicação IROG - Usinagem</t>
+  </si>
+  <si>
+    <t>9471976034</t>
+  </si>
+  <si>
+    <t>Planejamento de capacidade MOxdemanda de preventivas no sistema de manutenção</t>
+  </si>
+  <si>
+    <t>9472588178</t>
+  </si>
+  <si>
+    <t>Divergência valores de vendas</t>
+  </si>
+  <si>
+    <t>Fazendo</t>
+  </si>
+  <si>
+    <t>9471986396</t>
+  </si>
+  <si>
+    <t>Melhoria Sistema de Custeio - Usinagem Pintura</t>
+  </si>
+  <si>
+    <t>9472038820</t>
+  </si>
+  <si>
+    <t>Códigos dos materiais - Definição do Escopo</t>
+  </si>
+  <si>
+    <t>9472051193</t>
+  </si>
+  <si>
+    <t>Atualização no Campo de Prioridade – Inclusão de SLA de Atendimento</t>
+  </si>
+  <si>
+    <t>9472066205</t>
+  </si>
+  <si>
+    <t>Carga H2 - Sistema de corridas</t>
+  </si>
+  <si>
+    <t>9472084271</t>
+  </si>
+  <si>
+    <t>Motivos de refugos</t>
+  </si>
+  <si>
+    <t>Impedimento</t>
+  </si>
+  <si>
+    <t>9472117689</t>
+  </si>
+  <si>
+    <t>Cadastro de padrões para Procedimento de Pintura (P.P.)</t>
+  </si>
+  <si>
+    <t>29/06/2025</t>
+  </si>
+  <si>
+    <t>9472122652</t>
+  </si>
+  <si>
+    <t>Segregação de funções</t>
+  </si>
+  <si>
+    <t>9472126049</t>
+  </si>
+  <si>
+    <t>Ajustar planilha</t>
+  </si>
+  <si>
+    <t>9472129437</t>
+  </si>
+  <si>
+    <t>Ajuste tela de processos</t>
+  </si>
+  <si>
+    <t>9472133314</t>
+  </si>
+  <si>
+    <t>Tela para indicar medida de espessura - Fundo/Primer</t>
+  </si>
+  <si>
+    <t>9472136615</t>
+  </si>
+  <si>
+    <t>Tela para indicar medida de espessura - Acabamento/Top Coat</t>
+  </si>
+  <si>
+    <t>9472141661</t>
+  </si>
+  <si>
+    <t>Ajuste registro principal da pintura</t>
+  </si>
+  <si>
+    <t>9480726359</t>
+  </si>
+  <si>
+    <t>Controle do status por declaração</t>
+  </si>
+  <si>
+    <t>9480736960</t>
+  </si>
+  <si>
+    <t>Projeto</t>
+  </si>
+  <si>
+    <t>Diário do bordo Ajustagem - Leitura de Tempo por Cabine</t>
+  </si>
+  <si>
+    <t>9503659366</t>
+  </si>
+  <si>
+    <t>Estruturar integração de clientes e ofertas com CRM</t>
+  </si>
+  <si>
+    <t>Semana 1</t>
+  </si>
+  <si>
+    <t>Julho</t>
+  </si>
+  <si>
+    <t>9480740893</t>
+  </si>
+  <si>
+    <t>Apontamento Quebra de Canal - Homologação</t>
+  </si>
+  <si>
+    <t>9480756329</t>
+  </si>
+  <si>
+    <t>Apontamento eletrônico corte pó de ferro  - Homologação</t>
+  </si>
+  <si>
+    <t>9480759066</t>
+  </si>
+  <si>
+    <t>Planilha - Controle de OSs - Instalação Industrial - Importar Planilha</t>
+  </si>
+  <si>
+    <t>9480766060</t>
+  </si>
+  <si>
+    <t>Mapeamento de Solda - Reunião</t>
+  </si>
+  <si>
+    <t>9480789768</t>
+  </si>
+  <si>
+    <t>Criar alerta no Lançamento da NF para verificar se ha horário agendado</t>
+  </si>
+  <si>
+    <t>30012</t>
+  </si>
+  <si>
+    <t>PCP</t>
+  </si>
+  <si>
+    <t>Saneamento de dados para APS e treinamento</t>
+  </si>
+  <si>
+    <t>Objetivo: alimentar dados mestres nas tabelas do APS 8-9. Levantamento de informações para a especificação funcional do projeto. ( TI especificação de interface inicial) REALIZADO @Edson João Hammermeister por favor indicar tempo para essa atividade. Atenciosamente, De: João Pedro Beccon Enviada em:</t>
+  </si>
+  <si>
+    <t>João Pedro Beccon</t>
   </si>
   <si>
     <t>Sistemas</t>
   </si>
   <si>
-    <t>09/03/2026</t>
-  </si>
-  <si>
-    <t>32134</t>
-  </si>
-  <si>
-    <t>Extensão da visão do relatório de busca de sequencias para depósito</t>
-  </si>
-  <si>
-    <t>Homologação</t>
-  </si>
-  <si>
-    <t>32219</t>
-  </si>
-  <si>
-    <t>Apontamento Ajustagem</t>
-  </si>
-  <si>
-    <t>32319</t>
-  </si>
-  <si>
-    <t>Códigos para Cadastro</t>
-  </si>
-  <si>
-    <t>18/06/2025</t>
-  </si>
-  <si>
-    <t>32111</t>
-  </si>
-  <si>
-    <t>Atualização sistema mapeamento</t>
-  </si>
-  <si>
-    <t>25310</t>
-  </si>
-  <si>
-    <t>Sistema de Controle de Orçamento de Entregas de Venda</t>
-  </si>
-  <si>
-    <t>Boa Tarde Segue anexo escopo para criação do sistema de controle de orçamentos de Entrega de venda, para comparação com o realizado e provisionamento de custo para a controladoria.</t>
-  </si>
-  <si>
-    <t>26/05/2025</t>
-  </si>
-  <si>
-    <t>Semana 4</t>
-  </si>
-  <si>
-    <t>32200</t>
-  </si>
-  <si>
-    <t>Dados retroativos Qlick Sense</t>
-  </si>
-  <si>
-    <t>26/06/2025</t>
-  </si>
-  <si>
-    <t>23838</t>
-  </si>
-  <si>
-    <t>Novo Sistema</t>
-  </si>
-  <si>
-    <t>Criar agendamento de remessa para industrialização - Reunião</t>
-  </si>
-  <si>
-    <t>32545</t>
-  </si>
-  <si>
-    <t>Exclusão de Entrega de EPI</t>
-  </si>
-  <si>
-    <t>27/06/2025</t>
-  </si>
-  <si>
-    <t>32538</t>
-  </si>
-  <si>
-    <t>ESTORNO 88890</t>
-  </si>
-  <si>
-    <t>32530</t>
-  </si>
-  <si>
-    <t>Alteração na Aplicação - "Requisição"</t>
-  </si>
-  <si>
-    <t>32529</t>
-  </si>
-  <si>
-    <t>Horímetro - Apontamento eletrônico Manipuladores</t>
-  </si>
-  <si>
-    <t>32507</t>
-  </si>
-  <si>
-    <t>Adequação no SMI para uso do Preset (Acabamento)</t>
-  </si>
-  <si>
-    <t>32506</t>
-  </si>
-  <si>
-    <t>[COMPRAS] Criação campo Forma de Pagamento - na tela de Cadastro de Fornecedo</t>
-  </si>
-  <si>
-    <t>32505</t>
-  </si>
-  <si>
-    <t>Alteração na emissão de notas de remessa</t>
-  </si>
-  <si>
-    <t>32485</t>
-  </si>
-  <si>
-    <t>Tempos dos modelos UPR</t>
-  </si>
-  <si>
-    <t>32482</t>
-  </si>
-  <si>
-    <t>Correção</t>
-  </si>
-  <si>
-    <t>Validação Solda - QlikSense</t>
-  </si>
-  <si>
-    <t>32474</t>
-  </si>
-  <si>
-    <t>Divergência no tempo padrão rateio - IROG Usinagem</t>
-  </si>
-  <si>
-    <t>32472</t>
-  </si>
-  <si>
-    <t>Desenvolvimento de BI de apontamento</t>
-  </si>
-  <si>
-    <t>32467</t>
-  </si>
-  <si>
-    <t>Informações QlikSense para engenharia</t>
-  </si>
-  <si>
-    <t>32457</t>
-  </si>
-  <si>
-    <t>Apareça o contentor</t>
-  </si>
-  <si>
-    <t>32456</t>
-  </si>
-  <si>
-    <t>Tela de pedido de compra</t>
-  </si>
-  <si>
-    <t>32455</t>
-  </si>
-  <si>
-    <t>Sistema de inventario</t>
-  </si>
-  <si>
-    <t>32435</t>
-  </si>
-  <si>
-    <t>Consulta de Pedido de Compra Nimbi</t>
-  </si>
-  <si>
-    <t>32432</t>
-  </si>
-  <si>
-    <t>[NIMBI] INTEGRAÇÃO DE IMPOSTOS NOS PEDIDOS</t>
-  </si>
-  <si>
-    <t>32423</t>
-  </si>
-  <si>
-    <t>Solicitação de colunas informando horário/quantidades de peças</t>
-  </si>
-  <si>
-    <t>32422</t>
-  </si>
-  <si>
-    <t>Solicitação de criação de área para acompanhamento de pedidos</t>
-  </si>
-  <si>
-    <t>32400</t>
-  </si>
-  <si>
-    <t>Solicitação quantidade de peça a ser coleta nesta tela</t>
-  </si>
-  <si>
-    <t>32387</t>
-  </si>
-  <si>
-    <t>Desenvolvimento de gráfico - aplicação Refugo Qlik Sense</t>
-  </si>
-  <si>
-    <t>32376</t>
-  </si>
-  <si>
-    <t>Alteração aplicação IROG - Usinagem</t>
-  </si>
-  <si>
-    <t>32363</t>
-  </si>
-  <si>
-    <t>Planejamento de capacidade MOxdemanda de preventivas no sistema de manutenção</t>
-  </si>
-  <si>
-    <t>9472588178</t>
-  </si>
-  <si>
-    <t>Divergência valores de vendas</t>
-  </si>
-  <si>
-    <t>Fazendo</t>
-  </si>
-  <si>
-    <t>32353</t>
-  </si>
-  <si>
-    <t>Melhoria Sistema de Custeio - Usinagem Pintura</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Alexandre, bom dia! Para Custeio Usinagem Pintura, ao invés de utilizar apontamentos de horas, valores do setor PINTURA (centro custo 8010) devem ser rateados somente para as sequências movimentadas no setor 3081. Critério de rateio deve ser proporcional de custo FTF dos setores 3081 + 3082 + 8010. </t>
-  </si>
-  <si>
-    <t>Paulo Giovani da Cruz</t>
-  </si>
-  <si>
-    <t>32348</t>
-  </si>
-  <si>
-    <t>Códigos dos materiais - Definição do Escopo</t>
-  </si>
-  <si>
-    <t>32346</t>
-  </si>
-  <si>
-    <t>Atualização no Campo de Prioridade – Inclusão de SLA de Atendimento</t>
-  </si>
-  <si>
-    <t>32325</t>
-  </si>
-  <si>
-    <t>Carga H2 - Sistema de corridas</t>
-  </si>
-  <si>
-    <t>32310</t>
-  </si>
-  <si>
-    <t>Motivos de refugos</t>
-  </si>
-  <si>
-    <t>Impedimento</t>
-  </si>
-  <si>
-    <t>19909</t>
-  </si>
-  <si>
-    <t>Cadastro de padrões para Procedimento de Pintura (P.P.)</t>
-  </si>
-  <si>
-    <t>Segregação de funções</t>
-  </si>
-  <si>
-    <t>Ajustar planilha</t>
-  </si>
-  <si>
-    <t>Ajuste tela de processos</t>
-  </si>
-  <si>
-    <t>Tela para indicar medida de espessura - Fundo/Primer</t>
-  </si>
-  <si>
-    <t>Tela para indicar medida de espessura - Acabamento/Top Coat</t>
-  </si>
-  <si>
-    <t>Ajuste registro principal da pintura</t>
-  </si>
-  <si>
-    <t>30903</t>
-  </si>
-  <si>
-    <t>Controle do status por declaração</t>
-  </si>
-  <si>
-    <t>30/06/2025</t>
-  </si>
-  <si>
-    <t>29095</t>
-  </si>
-  <si>
-    <t>Projeto</t>
-  </si>
-  <si>
-    <t>Diário do bordo Ajustagem - Leitura de Tempo por Cabine</t>
-  </si>
-  <si>
-    <t>9503659366</t>
-  </si>
-  <si>
-    <t>Estruturar integração de clientes e ofertas com CRM</t>
-  </si>
-  <si>
-    <t>02/07/2025</t>
-  </si>
-  <si>
-    <t>Semana 1</t>
-  </si>
-  <si>
-    <t>Julho</t>
-  </si>
-  <si>
-    <t>9480740893</t>
-  </si>
-  <si>
-    <t>Apontamento Quebra de Canal - Homologação</t>
-  </si>
-  <si>
-    <t>31292</t>
-  </si>
-  <si>
-    <t>Apontamento eletrônico corte pó de ferro  - Homologação</t>
-  </si>
-  <si>
-    <t>32113</t>
-  </si>
-  <si>
-    <t>Planilha - Controle de OSs - Instalação Industrial - Importar Planilha</t>
-  </si>
-  <si>
-    <t>32298</t>
-  </si>
-  <si>
-    <t>Mapeamento de Solda - Reunião</t>
-  </si>
-  <si>
-    <t>Criar alerta no Lançamento da NF para verificar se ha horário agendado</t>
-  </si>
-  <si>
-    <t>30012</t>
-  </si>
-  <si>
-    <t>Saneamento de dados para APS e treinamento</t>
-  </si>
-  <si>
-    <t>Objetivo: alimentar dados mestres nas tabelas do APS 8-9. Levantamento de informações para a especificação funcional do projeto. ( TI especificação de interface inicial) REALIZADO @Edson João Hammermeister por favor indicar tempo para essa atividade. Atenciosamente, De: João Pedro Beccon Enviada em:</t>
-  </si>
-  <si>
-    <t>João Pedro Beccon</t>
-  </si>
-  <si>
     <t>19/05/2026</t>
   </si>
   <si>
+    <t>9481930634</t>
+  </si>
+  <si>
     <t>Gravar dados na tabela VD057</t>
   </si>
   <si>
-    <t>32287</t>
+    <t>9480859941</t>
   </si>
   <si>
     <t>Aplicação de controle de consumo e custo de PROEX e Antecipação de Caterpillar - Reunião</t>
   </si>
   <si>
+    <t>9481933895</t>
+  </si>
+  <si>
     <t>Notificação via e-mail para o transportador ao registrar uma ordem de coleta</t>
   </si>
   <si>
-    <t>28583</t>
+    <t>9480878405</t>
   </si>
   <si>
     <t>Compara Carteira UPR - Erro (copy)</t>
   </si>
   <si>
-    <t>31699</t>
+    <t>9480975363</t>
   </si>
   <si>
     <t>Copiloto Gerencial IA - Descrição das Tabelas</t>
   </si>
   <si>
-    <t>31529</t>
+    <t>9481027476</t>
   </si>
   <si>
     <t>Pré-lista em cascata, por endereço</t>
   </si>
   <si>
-    <t>31836</t>
+    <t>9481027666</t>
   </si>
   <si>
     <t>Melhoria WMS - Conferencia e Carregamento</t>
@@ -582,91 +624,100 @@
     <t>Boa tarde Vou assumir a importação da empresa e gostaria de criar um sistema de controle das Importações: Escopo principal: * Tela com todos as OC para importação - Liberação de Suprimentos para Logistica * Cadastro de processo (informações direto da OC) * Cadastro e controle de datas de embarques (</t>
   </si>
   <si>
+    <t>9481027865</t>
+  </si>
+  <si>
     <t>Mapeamento Digital</t>
   </si>
   <si>
-    <t>24746</t>
+    <t>9481027941</t>
   </si>
   <si>
     <t>Integração de faturamentos com eventos</t>
   </si>
   <si>
-    <t>31233</t>
+    <t>9481042949</t>
   </si>
   <si>
     <t>Integração faturamento x Benner  Reunião de entrega</t>
   </si>
   <si>
-    <t>30796</t>
+    <t>9481047692</t>
   </si>
   <si>
     <t>Sistema gestão de ações</t>
   </si>
   <si>
-    <t>31977</t>
+    <t>9481074264</t>
   </si>
   <si>
     <t>Alterações no registro de moldagem via APP</t>
   </si>
   <si>
-    <t>32077</t>
+    <t>9481074503</t>
   </si>
   <si>
     <t>alterar informações de romaneio e quantidade</t>
   </si>
   <si>
-    <t>31015</t>
+    <t>9481074850</t>
   </si>
   <si>
     <t>Conversão KB TOTO</t>
   </si>
   <si>
+    <t>9481850741</t>
+  </si>
+  <si>
     <t>Mapeamento de Solda - Apontamento</t>
   </si>
   <si>
+    <t>9481890129</t>
+  </si>
+  <si>
     <t>Retrabalho da moldagem - Reunião</t>
   </si>
   <si>
     <t>Cadastro de Fornecedores/Serviço</t>
   </si>
   <si>
-    <t>01/07/2025</t>
+    <t>9496586508</t>
   </si>
   <si>
     <t>Mapeamento de Solda - Relatório</t>
   </si>
   <si>
-    <t>31092</t>
+    <t>9502871921</t>
   </si>
   <si>
     <t>Etiquetas corpo de prova</t>
   </si>
   <si>
-    <t>32271</t>
+    <t>9502872000</t>
   </si>
   <si>
     <t>Ajustar a baixa de oferta quando foi perdida/cancelada e Alterar os relatórios de Orçamentos Cancelados e Perdid (copy)</t>
   </si>
   <si>
-    <t>32265</t>
+    <t>9502872091</t>
   </si>
   <si>
     <t>Atualização apontamento eletrônico manipuladores</t>
   </si>
   <si>
-    <t>31257</t>
+    <t>9502872135</t>
   </si>
   <si>
     <t>Máquina de Ensaios</t>
   </si>
   <si>
-    <t>31520</t>
+    <t>9502872035</t>
   </si>
   <si>
     <t>Sistema tablet acabamento linhas UPR</t>
   </si>
   <si>
-    <t>32667</t>
+    <t>9522344289</t>
   </si>
   <si>
     <t>ALTERAÇÃO DE FLUXO - PEÇA PARA ENSAIO MECÂNICO</t>
@@ -687,7 +738,7 @@
     <t>14/07/2025</t>
   </si>
   <si>
-    <t>32333</t>
+    <t>9586703054</t>
   </si>
   <si>
     <t>Relatório Invoices x OTF x Modelo</t>
@@ -702,7 +753,7 @@
     <t>Boa tarde Conforme conversamos, precisamos de um sistema dentro do WMS que faça a distribuição em tempo real do saldo do Estoque com a carteira. Conforme é realizado o faturamento, a carteira seja atualizada em tempo real, bem como a entrada e estorno do material. O sistema deve fornecer um relatóri</t>
   </si>
   <si>
-    <t>26428</t>
+    <t>9586703294</t>
   </si>
   <si>
     <t>CONSULTA EMBARQUES ALTONA</t>
@@ -714,7 +765,7 @@
     <t>Período</t>
   </si>
   <si>
-    <t>SPRINT 2025-14</t>
+    <t>Mai/2025</t>
   </si>
   <si>
     <t>Base</t>
@@ -1350,13 +1401,13 @@
         <v>31</v>
       </c>
       <c r="K3" s="2" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="L3" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="M3" s="2" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="N3" s="2" t="s">
         <v>34</v>
@@ -1397,7 +1448,7 @@
         <v>23</v>
       </c>
       <c r="K4" s="2" t="s">
-        <v>24</v>
+        <v>39</v>
       </c>
       <c r="L4" s="2" t="s">
         <v>25</v>
@@ -1414,37 +1465,37 @@
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>16</v>
+        <v>41</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>17</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>38</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>31</v>
       </c>
       <c r="K5" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="L5" s="2" t="s">
         <v>25</v>
@@ -1461,7 +1512,7 @@
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>16</v>
@@ -1473,10 +1524,10 @@
         <v>18</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>38</v>
@@ -1488,10 +1539,10 @@
         <v>22</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="K6" s="2" t="s">
-        <v>24</v>
+        <v>39</v>
       </c>
       <c r="L6" s="2" t="s">
         <v>25</v>
@@ -1500,7 +1551,7 @@
         <v>26</v>
       </c>
       <c r="N6" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="O6" s="2" t="s">
         <v>28</v>
@@ -1508,7 +1559,7 @@
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>16</v>
@@ -1517,28 +1568,28 @@
         <v>17</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>40</v>
+        <v>18</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>38</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>53</v>
+        <v>21</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>54</v>
+        <v>22</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>31</v>
       </c>
       <c r="K7" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="L7" s="2" t="s">
         <v>25</v>
@@ -1555,22 +1606,22 @@
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E8" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="B8" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>57</v>
-      </c>
       <c r="F8" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>38</v>
@@ -1585,13 +1636,13 @@
         <v>31</v>
       </c>
       <c r="K8" s="2" t="s">
-        <v>24</v>
+        <v>39</v>
       </c>
       <c r="L8" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="M8" s="2" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="N8" s="2" t="s">
         <v>34</v>
@@ -1602,22 +1653,22 @@
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E9" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="B9" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>60</v>
-      </c>
       <c r="F9" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G9" s="2" t="s">
         <v>38</v>
@@ -1632,7 +1683,7 @@
         <v>31</v>
       </c>
       <c r="K9" s="2" t="s">
-        <v>24</v>
+        <v>60</v>
       </c>
       <c r="L9" s="2" t="s">
         <v>25</v>
@@ -1679,7 +1730,7 @@
         <v>63</v>
       </c>
       <c r="K10" s="2" t="s">
-        <v>24</v>
+        <v>54</v>
       </c>
       <c r="L10" s="2" t="s">
         <v>25</v>
@@ -1688,7 +1739,7 @@
         <v>26</v>
       </c>
       <c r="N10" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="O10" s="2" t="s">
         <v>35</v>
@@ -1746,13 +1797,13 @@
         <v>66</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>16</v>
+        <v>41</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>17</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>67</v>
@@ -1764,16 +1815,16 @@
         <v>38</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>69</v>
       </c>
       <c r="K12" s="2" t="s">
-        <v>24</v>
+        <v>39</v>
       </c>
       <c r="L12" s="2" t="s">
         <v>25</v>
@@ -1820,7 +1871,7 @@
         <v>73</v>
       </c>
       <c r="K13" s="2" t="s">
-        <v>24</v>
+        <v>60</v>
       </c>
       <c r="L13" s="2" t="s">
         <v>25</v>
@@ -1864,10 +1915,10 @@
         <v>22</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="K14" s="2" t="s">
-        <v>24</v>
+        <v>77</v>
       </c>
       <c r="L14" s="2" t="s">
         <v>25</v>
@@ -1876,7 +1927,7 @@
         <v>26</v>
       </c>
       <c r="N14" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="O14" s="2" t="s">
         <v>28</v>
@@ -1884,7 +1935,7 @@
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>16</v>
@@ -1896,10 +1947,10 @@
         <v>18</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G15" s="2" t="s">
         <v>38</v>
@@ -1911,10 +1962,10 @@
         <v>22</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="K15" s="2" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="L15" s="2" t="s">
         <v>25</v>
@@ -1931,34 +1982,34 @@
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I16" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="J16" s="2" t="s">
         <v>80</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="E16" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="F16" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="G16" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="H16" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="I16" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="J16" s="2" t="s">
-        <v>79</v>
       </c>
       <c r="K16" s="2" t="s">
         <v>24</v>
@@ -1978,7 +2029,7 @@
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>16</v>
@@ -1990,10 +2041,10 @@
         <v>18</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="G17" s="2" t="s">
         <v>38</v>
@@ -2005,10 +2056,10 @@
         <v>22</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="K17" s="2" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="L17" s="2" t="s">
         <v>25</v>
@@ -2025,7 +2076,7 @@
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>16</v>
@@ -2037,10 +2088,10 @@
         <v>18</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="G18" s="2" t="s">
         <v>38</v>
@@ -2052,10 +2103,10 @@
         <v>22</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="K18" s="2" t="s">
-        <v>24</v>
+        <v>39</v>
       </c>
       <c r="L18" s="2" t="s">
         <v>25</v>
@@ -2072,7 +2123,7 @@
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>16</v>
@@ -2084,10 +2135,10 @@
         <v>18</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G19" s="2" t="s">
         <v>38</v>
@@ -2099,10 +2150,10 @@
         <v>22</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="K19" s="2" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="L19" s="2" t="s">
         <v>25</v>
@@ -2119,7 +2170,7 @@
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>16</v>
@@ -2131,10 +2182,10 @@
         <v>18</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G20" s="2" t="s">
         <v>38</v>
@@ -2146,10 +2197,10 @@
         <v>22</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="K20" s="2" t="s">
-        <v>24</v>
+        <v>91</v>
       </c>
       <c r="L20" s="2" t="s">
         <v>25</v>
@@ -2166,7 +2217,7 @@
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>16</v>
@@ -2178,10 +2229,10 @@
         <v>18</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="G21" s="2" t="s">
         <v>38</v>
@@ -2193,10 +2244,10 @@
         <v>22</v>
       </c>
       <c r="J21" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="K21" s="2" t="s">
-        <v>24</v>
+        <v>94</v>
       </c>
       <c r="L21" s="2" t="s">
         <v>25</v>
@@ -2213,7 +2264,7 @@
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>16</v>
@@ -2225,10 +2276,10 @@
         <v>18</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="G22" s="2" t="s">
         <v>20</v>
@@ -2240,10 +2291,10 @@
         <v>22</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="K22" s="2" t="s">
-        <v>24</v>
+        <v>91</v>
       </c>
       <c r="L22" s="2" t="s">
         <v>25</v>
@@ -2260,22 +2311,22 @@
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="D23" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="G23" s="2" t="s">
         <v>38</v>
@@ -2287,10 +2338,10 @@
         <v>22</v>
       </c>
       <c r="J23" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="K23" s="2" t="s">
-        <v>24</v>
+        <v>100</v>
       </c>
       <c r="L23" s="2" t="s">
         <v>25</v>
@@ -2307,22 +2358,22 @@
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="D24" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="G24" s="2" t="s">
         <v>20</v>
@@ -2334,10 +2385,10 @@
         <v>22</v>
       </c>
       <c r="J24" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="K24" s="2" t="s">
-        <v>24</v>
+        <v>91</v>
       </c>
       <c r="L24" s="2" t="s">
         <v>25</v>
@@ -2354,7 +2405,7 @@
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>16</v>
@@ -2366,10 +2417,10 @@
         <v>18</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="G25" s="2" t="s">
         <v>38</v>
@@ -2381,10 +2432,10 @@
         <v>22</v>
       </c>
       <c r="J25" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="K25" s="2" t="s">
-        <v>24</v>
+        <v>105</v>
       </c>
       <c r="L25" s="2" t="s">
         <v>25</v>
@@ -2401,7 +2452,7 @@
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>16</v>
@@ -2413,10 +2464,10 @@
         <v>18</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="G26" s="2" t="s">
         <v>38</v>
@@ -2428,10 +2479,10 @@
         <v>22</v>
       </c>
       <c r="J26" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="K26" s="2" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="L26" s="2" t="s">
         <v>25</v>
@@ -2448,7 +2499,7 @@
     </row>
     <row r="27" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="B27" s="2" t="s">
         <v>16</v>
@@ -2460,10 +2511,10 @@
         <v>18</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="G27" s="2" t="s">
         <v>38</v>
@@ -2475,10 +2526,10 @@
         <v>22</v>
       </c>
       <c r="J27" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="K27" s="2" t="s">
-        <v>24</v>
+        <v>54</v>
       </c>
       <c r="L27" s="2" t="s">
         <v>25</v>
@@ -2495,7 +2546,7 @@
     </row>
     <row r="28" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="B28" s="2" t="s">
         <v>16</v>
@@ -2507,10 +2558,10 @@
         <v>18</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="G28" s="2" t="s">
         <v>38</v>
@@ -2522,10 +2573,10 @@
         <v>22</v>
       </c>
       <c r="J28" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="K28" s="2" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="L28" s="2" t="s">
         <v>25</v>
@@ -2542,7 +2593,7 @@
     </row>
     <row r="29" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="B29" s="2" t="s">
         <v>16</v>
@@ -2554,10 +2605,10 @@
         <v>18</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="G29" s="2" t="s">
         <v>38</v>
@@ -2569,10 +2620,10 @@
         <v>22</v>
       </c>
       <c r="J29" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="K29" s="2" t="s">
-        <v>24</v>
+        <v>94</v>
       </c>
       <c r="L29" s="2" t="s">
         <v>25</v>
@@ -2589,7 +2640,7 @@
     </row>
     <row r="30" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="B30" s="2" t="s">
         <v>16</v>
@@ -2601,10 +2652,10 @@
         <v>18</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="G30" s="2" t="s">
         <v>38</v>
@@ -2616,10 +2667,10 @@
         <v>22</v>
       </c>
       <c r="J30" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="K30" s="2" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="L30" s="2" t="s">
         <v>25</v>
@@ -2636,7 +2687,7 @@
     </row>
     <row r="31" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="B31" s="2" t="s">
         <v>16</v>
@@ -2648,10 +2699,10 @@
         <v>18</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="G31" s="2" t="s">
         <v>38</v>
@@ -2663,10 +2714,10 @@
         <v>22</v>
       </c>
       <c r="J31" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="K31" s="2" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="L31" s="2" t="s">
         <v>25</v>
@@ -2683,7 +2734,7 @@
     </row>
     <row r="32" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="B32" s="2" t="s">
         <v>16</v>
@@ -2695,10 +2746,10 @@
         <v>18</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="G32" s="2" t="s">
         <v>38</v>
@@ -2710,10 +2761,10 @@
         <v>22</v>
       </c>
       <c r="J32" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="K32" s="2" t="s">
-        <v>24</v>
+        <v>54</v>
       </c>
       <c r="L32" s="2" t="s">
         <v>25</v>
@@ -2730,7 +2781,7 @@
     </row>
     <row r="33" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="B33" s="2" t="s">
         <v>16</v>
@@ -2742,10 +2793,10 @@
         <v>18</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="G33" s="2" t="s">
         <v>38</v>
@@ -2757,10 +2808,10 @@
         <v>22</v>
       </c>
       <c r="J33" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="K33" s="2" t="s">
-        <v>24</v>
+        <v>39</v>
       </c>
       <c r="L33" s="2" t="s">
         <v>25</v>
@@ -2777,7 +2828,7 @@
     </row>
     <row r="34" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="B34" s="2" t="s">
         <v>16</v>
@@ -2789,10 +2840,10 @@
         <v>18</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="G34" s="2" t="s">
         <v>38</v>
@@ -2804,10 +2855,10 @@
         <v>22</v>
       </c>
       <c r="J34" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="K34" s="2" t="s">
-        <v>24</v>
+        <v>54</v>
       </c>
       <c r="L34" s="2" t="s">
         <v>25</v>
@@ -2824,7 +2875,7 @@
     </row>
     <row r="35" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="B35" s="2" t="s">
         <v>16</v>
@@ -2836,10 +2887,10 @@
         <v>18</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="G35" s="2" t="s">
         <v>38</v>
@@ -2851,10 +2902,10 @@
         <v>22</v>
       </c>
       <c r="J35" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="K35" s="2" t="s">
-        <v>24</v>
+        <v>126</v>
       </c>
       <c r="L35" s="2" t="s">
         <v>25</v>
@@ -2871,7 +2922,7 @@
     </row>
     <row r="36" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
-        <v>121</v>
+        <v>127</v>
       </c>
       <c r="B36" s="2" t="s">
         <v>16</v>
@@ -2883,10 +2934,10 @@
         <v>18</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="G36" s="2" t="s">
         <v>38</v>
@@ -2898,10 +2949,10 @@
         <v>22</v>
       </c>
       <c r="J36" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="K36" s="2" t="s">
-        <v>24</v>
+        <v>60</v>
       </c>
       <c r="L36" s="2" t="s">
         <v>25</v>
@@ -2918,7 +2969,7 @@
     </row>
     <row r="37" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="B37" s="2" t="s">
         <v>16</v>
@@ -2930,10 +2981,10 @@
         <v>18</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>124</v>
+        <v>130</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>124</v>
+        <v>130</v>
       </c>
       <c r="G37" s="2" t="s">
         <v>38</v>
@@ -2945,10 +2996,10 @@
         <v>22</v>
       </c>
       <c r="J37" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="K37" s="2" t="s">
-        <v>24</v>
+        <v>39</v>
       </c>
       <c r="L37" s="2" t="s">
         <v>25</v>
@@ -2965,22 +3016,22 @@
     </row>
     <row r="38" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="B38" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="D38" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>126</v>
+        <v>132</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>126</v>
+        <v>132</v>
       </c>
       <c r="G38" s="2" t="s">
         <v>20</v>
@@ -2992,16 +3043,16 @@
         <v>22</v>
       </c>
       <c r="J38" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="K38" s="2" t="s">
-        <v>24</v>
+        <v>77</v>
       </c>
       <c r="L38" s="2" t="s">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="M38" s="2" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="N38" s="2" t="s">
         <v>70</v>
@@ -3012,7 +3063,7 @@
     </row>
     <row r="39" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
-        <v>128</v>
+        <v>134</v>
       </c>
       <c r="B39" s="2" t="s">
         <v>16</v>
@@ -3021,28 +3072,28 @@
         <v>17</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>40</v>
+        <v>18</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>129</v>
+        <v>135</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="G39" s="2" t="s">
         <v>38</v>
       </c>
       <c r="H39" s="2" t="s">
-        <v>131</v>
+        <v>21</v>
       </c>
       <c r="I39" s="2" t="s">
-        <v>54</v>
+        <v>22</v>
       </c>
       <c r="J39" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="K39" s="2" t="s">
-        <v>24</v>
+        <v>77</v>
       </c>
       <c r="L39" s="2" t="s">
         <v>25</v>
@@ -3059,7 +3110,7 @@
     </row>
     <row r="40" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="B40" s="2" t="s">
         <v>16</v>
@@ -3071,10 +3122,10 @@
         <v>18</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="G40" s="2" t="s">
         <v>20</v>
@@ -3086,16 +3137,16 @@
         <v>22</v>
       </c>
       <c r="J40" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="K40" s="2" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="L40" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="M40" s="2" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="N40" s="2" t="s">
         <v>70</v>
@@ -3106,7 +3157,7 @@
     </row>
     <row r="41" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="B41" s="2" t="s">
         <v>16</v>
@@ -3118,10 +3169,10 @@
         <v>18</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="G41" s="2" t="s">
         <v>38</v>
@@ -3133,10 +3184,10 @@
         <v>22</v>
       </c>
       <c r="J41" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="K41" s="2" t="s">
-        <v>24</v>
+        <v>54</v>
       </c>
       <c r="L41" s="2" t="s">
         <v>25</v>
@@ -3153,7 +3204,7 @@
     </row>
     <row r="42" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="B42" s="2" t="s">
         <v>16</v>
@@ -3165,10 +3216,10 @@
         <v>18</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="G42" s="2" t="s">
         <v>38</v>
@@ -3180,10 +3231,10 @@
         <v>22</v>
       </c>
       <c r="J42" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="K42" s="2" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="L42" s="2" t="s">
         <v>25</v>
@@ -3200,7 +3251,7 @@
     </row>
     <row r="43" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="B43" s="2" t="s">
         <v>16</v>
@@ -3212,10 +3263,10 @@
         <v>18</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="F43" s="2" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="G43" s="2" t="s">
         <v>20</v>
@@ -3227,16 +3278,16 @@
         <v>22</v>
       </c>
       <c r="J43" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="K43" s="2" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="L43" s="2" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="M43" s="2" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="N43" s="2" t="s">
         <v>70</v>
@@ -3247,7 +3298,7 @@
     </row>
     <row r="44" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="B44" s="2" t="s">
         <v>16</v>
@@ -3259,10 +3310,10 @@
         <v>18</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="G44" s="2" t="s">
         <v>38</v>
@@ -3274,10 +3325,10 @@
         <v>22</v>
       </c>
       <c r="J44" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="K44" s="2" t="s">
-        <v>24</v>
+        <v>147</v>
       </c>
       <c r="L44" s="2" t="s">
         <v>25</v>
@@ -3294,7 +3345,7 @@
     </row>
     <row r="45" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
-        <v>141</v>
+        <v>148</v>
       </c>
       <c r="B45" s="2" t="s">
         <v>16</v>
@@ -3306,10 +3357,10 @@
         <v>18</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>143</v>
+        <v>149</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>143</v>
+        <v>149</v>
       </c>
       <c r="G45" s="2" t="s">
         <v>38</v>
@@ -3321,10 +3372,10 @@
         <v>22</v>
       </c>
       <c r="J45" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="K45" s="2" t="s">
-        <v>24</v>
+        <v>147</v>
       </c>
       <c r="L45" s="2" t="s">
         <v>25</v>
@@ -3341,7 +3392,7 @@
     </row>
     <row r="46" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
-        <v>141</v>
+        <v>150</v>
       </c>
       <c r="B46" s="2" t="s">
         <v>16</v>
@@ -3353,10 +3404,10 @@
         <v>18</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>144</v>
+        <v>151</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>144</v>
+        <v>151</v>
       </c>
       <c r="G46" s="2" t="s">
         <v>38</v>
@@ -3368,10 +3419,10 @@
         <v>22</v>
       </c>
       <c r="J46" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="K46" s="2" t="s">
-        <v>24</v>
+        <v>94</v>
       </c>
       <c r="L46" s="2" t="s">
         <v>25</v>
@@ -3388,7 +3439,7 @@
     </row>
     <row r="47" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
-        <v>141</v>
+        <v>152</v>
       </c>
       <c r="B47" s="2" t="s">
         <v>16</v>
@@ -3400,10 +3451,10 @@
         <v>18</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>145</v>
+        <v>153</v>
       </c>
       <c r="F47" s="2" t="s">
-        <v>145</v>
+        <v>153</v>
       </c>
       <c r="G47" s="2" t="s">
         <v>38</v>
@@ -3415,10 +3466,10 @@
         <v>22</v>
       </c>
       <c r="J47" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="K47" s="2" t="s">
-        <v>24</v>
+        <v>94</v>
       </c>
       <c r="L47" s="2" t="s">
         <v>25</v>
@@ -3435,7 +3486,7 @@
     </row>
     <row r="48" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A48" s="2" t="s">
-        <v>141</v>
+        <v>154</v>
       </c>
       <c r="B48" s="2" t="s">
         <v>16</v>
@@ -3447,10 +3498,10 @@
         <v>18</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>146</v>
+        <v>155</v>
       </c>
       <c r="F48" s="2" t="s">
-        <v>146</v>
+        <v>155</v>
       </c>
       <c r="G48" s="2" t="s">
         <v>38</v>
@@ -3462,10 +3513,10 @@
         <v>22</v>
       </c>
       <c r="J48" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="K48" s="2" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="L48" s="2" t="s">
         <v>25</v>
@@ -3482,7 +3533,7 @@
     </row>
     <row r="49" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
-        <v>141</v>
+        <v>156</v>
       </c>
       <c r="B49" s="2" t="s">
         <v>16</v>
@@ -3494,10 +3545,10 @@
         <v>18</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>147</v>
+        <v>157</v>
       </c>
       <c r="F49" s="2" t="s">
-        <v>147</v>
+        <v>157</v>
       </c>
       <c r="G49" s="2" t="s">
         <v>38</v>
@@ -3509,10 +3560,10 @@
         <v>22</v>
       </c>
       <c r="J49" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="K49" s="2" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="L49" s="2" t="s">
         <v>25</v>
@@ -3529,7 +3580,7 @@
     </row>
     <row r="50" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
-        <v>141</v>
+        <v>158</v>
       </c>
       <c r="B50" s="2" t="s">
         <v>16</v>
@@ -3541,10 +3592,10 @@
         <v>18</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>148</v>
+        <v>159</v>
       </c>
       <c r="F50" s="2" t="s">
-        <v>148</v>
+        <v>159</v>
       </c>
       <c r="G50" s="2" t="s">
         <v>38</v>
@@ -3556,10 +3607,10 @@
         <v>22</v>
       </c>
       <c r="J50" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="K50" s="2" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="L50" s="2" t="s">
         <v>25</v>
@@ -3576,7 +3627,7 @@
     </row>
     <row r="51" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A51" s="2" t="s">
-        <v>149</v>
+        <v>160</v>
       </c>
       <c r="B51" s="2" t="s">
         <v>16</v>
@@ -3588,10 +3639,10 @@
         <v>18</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>150</v>
+        <v>161</v>
       </c>
       <c r="F51" s="2" t="s">
-        <v>150</v>
+        <v>161</v>
       </c>
       <c r="G51" s="2" t="s">
         <v>38</v>
@@ -3603,16 +3654,16 @@
         <v>22</v>
       </c>
       <c r="J51" s="2" t="s">
-        <v>151</v>
+        <v>32</v>
       </c>
       <c r="K51" s="2" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="L51" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="M51" s="2" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="N51" s="2" t="s">
         <v>27</v>
@@ -3623,22 +3674,22 @@
     </row>
     <row r="52" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A52" s="2" t="s">
-        <v>152</v>
+        <v>162</v>
       </c>
       <c r="B52" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>153</v>
+        <v>163</v>
       </c>
       <c r="D52" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>154</v>
+        <v>164</v>
       </c>
       <c r="F52" s="2" t="s">
-        <v>154</v>
+        <v>164</v>
       </c>
       <c r="G52" s="2" t="s">
         <v>38</v>
@@ -3650,10 +3701,10 @@
         <v>22</v>
       </c>
       <c r="J52" s="2" t="s">
-        <v>151</v>
+        <v>32</v>
       </c>
       <c r="K52" s="2" t="s">
-        <v>24</v>
+        <v>94</v>
       </c>
       <c r="L52" s="2" t="s">
         <v>25</v>
@@ -3670,22 +3721,22 @@
     </row>
     <row r="53" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A53" s="2" t="s">
-        <v>155</v>
+        <v>165</v>
       </c>
       <c r="B53" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>153</v>
+        <v>163</v>
       </c>
       <c r="D53" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>156</v>
+        <v>166</v>
       </c>
       <c r="F53" s="2" t="s">
-        <v>156</v>
+        <v>166</v>
       </c>
       <c r="G53" s="2" t="s">
         <v>20</v>
@@ -3697,27 +3748,27 @@
         <v>22</v>
       </c>
       <c r="J53" s="2" t="s">
-        <v>157</v>
+        <v>91</v>
       </c>
       <c r="K53" s="2" t="s">
-        <v>24</v>
+        <v>77</v>
       </c>
       <c r="L53" s="2" t="s">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="M53" s="2" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="N53" s="2" t="s">
-        <v>158</v>
+        <v>167</v>
       </c>
       <c r="O53" s="2" t="s">
-        <v>159</v>
+        <v>168</v>
       </c>
     </row>
     <row r="54" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A54" s="2" t="s">
-        <v>160</v>
+        <v>169</v>
       </c>
       <c r="B54" s="2" t="s">
         <v>16</v>
@@ -3729,10 +3780,10 @@
         <v>18</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>161</v>
+        <v>170</v>
       </c>
       <c r="F54" s="2" t="s">
-        <v>161</v>
+        <v>170</v>
       </c>
       <c r="G54" s="2" t="s">
         <v>38</v>
@@ -3744,10 +3795,10 @@
         <v>22</v>
       </c>
       <c r="J54" s="2" t="s">
-        <v>151</v>
+        <v>32</v>
       </c>
       <c r="K54" s="2" t="s">
-        <v>24</v>
+        <v>77</v>
       </c>
       <c r="L54" s="2" t="s">
         <v>25</v>
@@ -3764,7 +3815,7 @@
     </row>
     <row r="55" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A55" s="2" t="s">
-        <v>162</v>
+        <v>171</v>
       </c>
       <c r="B55" s="2" t="s">
         <v>16</v>
@@ -3776,10 +3827,10 @@
         <v>18</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>163</v>
+        <v>172</v>
       </c>
       <c r="F55" s="2" t="s">
-        <v>163</v>
+        <v>172</v>
       </c>
       <c r="G55" s="2" t="s">
         <v>38</v>
@@ -3791,10 +3842,10 @@
         <v>22</v>
       </c>
       <c r="J55" s="2" t="s">
-        <v>151</v>
+        <v>32</v>
       </c>
       <c r="K55" s="2" t="s">
-        <v>24</v>
+        <v>77</v>
       </c>
       <c r="L55" s="2" t="s">
         <v>25</v>
@@ -3811,7 +3862,7 @@
     </row>
     <row r="56" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A56" s="2" t="s">
-        <v>164</v>
+        <v>173</v>
       </c>
       <c r="B56" s="2" t="s">
         <v>16</v>
@@ -3823,10 +3874,10 @@
         <v>18</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>165</v>
+        <v>174</v>
       </c>
       <c r="F56" s="2" t="s">
-        <v>165</v>
+        <v>174</v>
       </c>
       <c r="G56" s="2" t="s">
         <v>38</v>
@@ -3838,10 +3889,10 @@
         <v>22</v>
       </c>
       <c r="J56" s="2" t="s">
-        <v>151</v>
+        <v>32</v>
       </c>
       <c r="K56" s="2" t="s">
-        <v>24</v>
+        <v>77</v>
       </c>
       <c r="L56" s="2" t="s">
         <v>25</v>
@@ -3858,22 +3909,22 @@
     </row>
     <row r="57" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A57" s="2" t="s">
-        <v>166</v>
+        <v>175</v>
       </c>
       <c r="B57" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>153</v>
+        <v>163</v>
       </c>
       <c r="D57" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>167</v>
+        <v>176</v>
       </c>
       <c r="F57" s="2" t="s">
-        <v>167</v>
+        <v>176</v>
       </c>
       <c r="G57" s="2" t="s">
         <v>20</v>
@@ -3885,10 +3936,10 @@
         <v>22</v>
       </c>
       <c r="J57" s="2" t="s">
-        <v>151</v>
+        <v>32</v>
       </c>
       <c r="K57" s="2" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="L57" s="2" t="s">
         <v>25</v>
@@ -3905,7 +3956,7 @@
     </row>
     <row r="58" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A58" s="2" t="s">
-        <v>74</v>
+        <v>177</v>
       </c>
       <c r="B58" s="2" t="s">
         <v>16</v>
@@ -3917,10 +3968,10 @@
         <v>18</v>
       </c>
       <c r="E58" s="2" t="s">
-        <v>168</v>
+        <v>178</v>
       </c>
       <c r="F58" s="2" t="s">
-        <v>168</v>
+        <v>178</v>
       </c>
       <c r="G58" s="2" t="s">
         <v>38</v>
@@ -3932,10 +3983,10 @@
         <v>22</v>
       </c>
       <c r="J58" s="2" t="s">
-        <v>151</v>
+        <v>32</v>
       </c>
       <c r="K58" s="2" t="s">
-        <v>24</v>
+        <v>77</v>
       </c>
       <c r="L58" s="2" t="s">
         <v>25</v>
@@ -3952,37 +4003,37 @@
     </row>
     <row r="59" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A59" s="2" t="s">
-        <v>169</v>
+        <v>179</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>16</v>
+        <v>180</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>153</v>
+        <v>163</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="E59" s="2" t="s">
-        <v>170</v>
+        <v>181</v>
       </c>
       <c r="F59" s="2" t="s">
-        <v>171</v>
+        <v>182</v>
       </c>
       <c r="G59" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H59" s="2" t="s">
-        <v>172</v>
+        <v>183</v>
       </c>
       <c r="I59" s="2" t="s">
-        <v>54</v>
+        <v>184</v>
       </c>
       <c r="J59" s="2" t="s">
-        <v>151</v>
+        <v>32</v>
       </c>
       <c r="K59" s="2" t="s">
-        <v>173</v>
+        <v>185</v>
       </c>
       <c r="L59" s="2" t="s">
         <v>25</v>
@@ -3999,7 +4050,7 @@
     </row>
     <row r="60" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A60" s="2" t="s">
-        <v>74</v>
+        <v>186</v>
       </c>
       <c r="B60" s="2" t="s">
         <v>16</v>
@@ -4011,10 +4062,10 @@
         <v>18</v>
       </c>
       <c r="E60" s="2" t="s">
-        <v>174</v>
+        <v>187</v>
       </c>
       <c r="F60" s="2" t="s">
-        <v>174</v>
+        <v>187</v>
       </c>
       <c r="G60" s="2" t="s">
         <v>38</v>
@@ -4026,10 +4077,10 @@
         <v>22</v>
       </c>
       <c r="J60" s="2" t="s">
-        <v>151</v>
+        <v>32</v>
       </c>
       <c r="K60" s="2" t="s">
-        <v>24</v>
+        <v>105</v>
       </c>
       <c r="L60" s="2" t="s">
         <v>25</v>
@@ -4046,22 +4097,22 @@
     </row>
     <row r="61" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A61" s="2" t="s">
-        <v>175</v>
+        <v>188</v>
       </c>
       <c r="B61" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>153</v>
+        <v>163</v>
       </c>
       <c r="D61" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>176</v>
+        <v>189</v>
       </c>
       <c r="F61" s="2" t="s">
-        <v>176</v>
+        <v>189</v>
       </c>
       <c r="G61" s="2" t="s">
         <v>38</v>
@@ -4073,16 +4124,16 @@
         <v>22</v>
       </c>
       <c r="J61" s="2" t="s">
-        <v>151</v>
+        <v>32</v>
       </c>
       <c r="K61" s="2" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="L61" s="2" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="M61" s="2" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="N61" s="2" t="s">
         <v>27</v>
@@ -4093,7 +4144,7 @@
     </row>
     <row r="62" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A62" s="2" t="s">
-        <v>74</v>
+        <v>190</v>
       </c>
       <c r="B62" s="2" t="s">
         <v>16</v>
@@ -4105,10 +4156,10 @@
         <v>18</v>
       </c>
       <c r="E62" s="2" t="s">
-        <v>177</v>
+        <v>191</v>
       </c>
       <c r="F62" s="2" t="s">
-        <v>177</v>
+        <v>191</v>
       </c>
       <c r="G62" s="2" t="s">
         <v>38</v>
@@ -4120,10 +4171,10 @@
         <v>22</v>
       </c>
       <c r="J62" s="2" t="s">
-        <v>151</v>
+        <v>32</v>
       </c>
       <c r="K62" s="2" t="s">
-        <v>24</v>
+        <v>105</v>
       </c>
       <c r="L62" s="2" t="s">
         <v>25</v>
@@ -4140,7 +4191,7 @@
     </row>
     <row r="63" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A63" s="2" t="s">
-        <v>178</v>
+        <v>192</v>
       </c>
       <c r="B63" s="2" t="s">
         <v>16</v>
@@ -4152,10 +4203,10 @@
         <v>18</v>
       </c>
       <c r="E63" s="2" t="s">
-        <v>179</v>
+        <v>193</v>
       </c>
       <c r="F63" s="2" t="s">
-        <v>179</v>
+        <v>193</v>
       </c>
       <c r="G63" s="2" t="s">
         <v>38</v>
@@ -4167,16 +4218,16 @@
         <v>22</v>
       </c>
       <c r="J63" s="2" t="s">
-        <v>151</v>
+        <v>32</v>
       </c>
       <c r="K63" s="2" t="s">
-        <v>24</v>
+        <v>39</v>
       </c>
       <c r="L63" s="2" t="s">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="M63" s="2" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="N63" s="2" t="s">
         <v>27</v>
@@ -4187,22 +4238,22 @@
     </row>
     <row r="64" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A64" s="2" t="s">
-        <v>180</v>
+        <v>194</v>
       </c>
       <c r="B64" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>153</v>
+        <v>163</v>
       </c>
       <c r="D64" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E64" s="2" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
       <c r="F64" s="2" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
       <c r="G64" s="2" t="s">
         <v>20</v>
@@ -4214,10 +4265,10 @@
         <v>22</v>
       </c>
       <c r="J64" s="2" t="s">
-        <v>151</v>
+        <v>32</v>
       </c>
       <c r="K64" s="2" t="s">
-        <v>24</v>
+        <v>39</v>
       </c>
       <c r="L64" s="2" t="s">
         <v>25</v>
@@ -4234,7 +4285,7 @@
     </row>
     <row r="65" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A65" s="2" t="s">
-        <v>182</v>
+        <v>196</v>
       </c>
       <c r="B65" s="2" t="s">
         <v>16</v>
@@ -4246,10 +4297,10 @@
         <v>18</v>
       </c>
       <c r="E65" s="2" t="s">
-        <v>183</v>
+        <v>197</v>
       </c>
       <c r="F65" s="2" t="s">
-        <v>183</v>
+        <v>197</v>
       </c>
       <c r="G65" s="2" t="s">
         <v>38</v>
@@ -4261,10 +4312,10 @@
         <v>22</v>
       </c>
       <c r="J65" s="2" t="s">
-        <v>151</v>
+        <v>32</v>
       </c>
       <c r="K65" s="2" t="s">
-        <v>24</v>
+        <v>126</v>
       </c>
       <c r="L65" s="2" t="s">
         <v>25</v>
@@ -4281,7 +4332,7 @@
     </row>
     <row r="66" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A66" s="2" t="s">
-        <v>184</v>
+        <v>198</v>
       </c>
       <c r="B66" s="2" t="s">
         <v>16</v>
@@ -4293,10 +4344,10 @@
         <v>18</v>
       </c>
       <c r="E66" s="2" t="s">
-        <v>185</v>
+        <v>199</v>
       </c>
       <c r="F66" s="2" t="s">
-        <v>185</v>
+        <v>199</v>
       </c>
       <c r="G66" s="2" t="s">
         <v>38</v>
@@ -4308,16 +4359,16 @@
         <v>22</v>
       </c>
       <c r="J66" s="2" t="s">
-        <v>151</v>
+        <v>32</v>
       </c>
       <c r="K66" s="2" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="L66" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="M66" s="2" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="N66" s="2" t="s">
         <v>27</v>
@@ -4328,37 +4379,37 @@
     </row>
     <row r="67" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A67" s="2" t="s">
-        <v>186</v>
+        <v>200</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>16</v>
+        <v>41</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>153</v>
+        <v>163</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="E67" s="2" t="s">
-        <v>187</v>
+        <v>201</v>
       </c>
       <c r="F67" s="2" t="s">
-        <v>188</v>
+        <v>202</v>
       </c>
       <c r="G67" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H67" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="I67" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="J67" s="2" t="s">
-        <v>151</v>
+        <v>32</v>
       </c>
       <c r="K67" s="2" t="s">
-        <v>24</v>
+        <v>39</v>
       </c>
       <c r="L67" s="2" t="s">
         <v>25</v>
@@ -4375,22 +4426,22 @@
     </row>
     <row r="68" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A68" s="2" t="s">
-        <v>166</v>
+        <v>203</v>
       </c>
       <c r="B68" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>153</v>
+        <v>163</v>
       </c>
       <c r="D68" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E68" s="2" t="s">
-        <v>189</v>
+        <v>204</v>
       </c>
       <c r="F68" s="2" t="s">
-        <v>189</v>
+        <v>204</v>
       </c>
       <c r="G68" s="2" t="s">
         <v>20</v>
@@ -4402,10 +4453,10 @@
         <v>22</v>
       </c>
       <c r="J68" s="2" t="s">
-        <v>151</v>
+        <v>32</v>
       </c>
       <c r="K68" s="2" t="s">
-        <v>24</v>
+        <v>94</v>
       </c>
       <c r="L68" s="2" t="s">
         <v>25</v>
@@ -4422,22 +4473,22 @@
     </row>
     <row r="69" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A69" s="2" t="s">
-        <v>190</v>
+        <v>205</v>
       </c>
       <c r="B69" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>153</v>
+        <v>163</v>
       </c>
       <c r="D69" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E69" s="2" t="s">
-        <v>191</v>
+        <v>206</v>
       </c>
       <c r="F69" s="2" t="s">
-        <v>191</v>
+        <v>206</v>
       </c>
       <c r="G69" s="2" t="s">
         <v>38</v>
@@ -4449,16 +4500,16 @@
         <v>22</v>
       </c>
       <c r="J69" s="2" t="s">
-        <v>151</v>
+        <v>32</v>
       </c>
       <c r="K69" s="2" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="L69" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="M69" s="2" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="N69" s="2" t="s">
         <v>27</v>
@@ -4469,7 +4520,7 @@
     </row>
     <row r="70" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A70" s="2" t="s">
-        <v>192</v>
+        <v>207</v>
       </c>
       <c r="B70" s="2" t="s">
         <v>16</v>
@@ -4481,10 +4532,10 @@
         <v>18</v>
       </c>
       <c r="E70" s="2" t="s">
-        <v>193</v>
+        <v>208</v>
       </c>
       <c r="F70" s="2" t="s">
-        <v>193</v>
+        <v>208</v>
       </c>
       <c r="G70" s="2" t="s">
         <v>38</v>
@@ -4496,16 +4547,16 @@
         <v>22</v>
       </c>
       <c r="J70" s="2" t="s">
-        <v>151</v>
+        <v>32</v>
       </c>
       <c r="K70" s="2" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="L70" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="M70" s="2" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="N70" s="2" t="s">
         <v>27</v>
@@ -4516,7 +4567,7 @@
     </row>
     <row r="71" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A71" s="2" t="s">
-        <v>194</v>
+        <v>209</v>
       </c>
       <c r="B71" s="2" t="s">
         <v>16</v>
@@ -4528,10 +4579,10 @@
         <v>18</v>
       </c>
       <c r="E71" s="2" t="s">
-        <v>195</v>
+        <v>210</v>
       </c>
       <c r="F71" s="2" t="s">
-        <v>195</v>
+        <v>210</v>
       </c>
       <c r="G71" s="2" t="s">
         <v>38</v>
@@ -4543,10 +4594,10 @@
         <v>22</v>
       </c>
       <c r="J71" s="2" t="s">
-        <v>151</v>
+        <v>32</v>
       </c>
       <c r="K71" s="2" t="s">
-        <v>24</v>
+        <v>91</v>
       </c>
       <c r="L71" s="2" t="s">
         <v>25</v>
@@ -4563,7 +4614,7 @@
     </row>
     <row r="72" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A72" s="2" t="s">
-        <v>196</v>
+        <v>211</v>
       </c>
       <c r="B72" s="2" t="s">
         <v>16</v>
@@ -4575,10 +4626,10 @@
         <v>18</v>
       </c>
       <c r="E72" s="2" t="s">
-        <v>197</v>
+        <v>212</v>
       </c>
       <c r="F72" s="2" t="s">
-        <v>197</v>
+        <v>212</v>
       </c>
       <c r="G72" s="2" t="s">
         <v>20</v>
@@ -4590,10 +4641,10 @@
         <v>22</v>
       </c>
       <c r="J72" s="2" t="s">
-        <v>151</v>
+        <v>32</v>
       </c>
       <c r="K72" s="2" t="s">
-        <v>24</v>
+        <v>39</v>
       </c>
       <c r="L72" s="2" t="s">
         <v>25</v>
@@ -4610,7 +4661,7 @@
     </row>
     <row r="73" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A73" s="2" t="s">
-        <v>198</v>
+        <v>213</v>
       </c>
       <c r="B73" s="2" t="s">
         <v>16</v>
@@ -4622,10 +4673,10 @@
         <v>18</v>
       </c>
       <c r="E73" s="2" t="s">
-        <v>199</v>
+        <v>214</v>
       </c>
       <c r="F73" s="2" t="s">
-        <v>199</v>
+        <v>214</v>
       </c>
       <c r="G73" s="2" t="s">
         <v>38</v>
@@ -4637,10 +4688,10 @@
         <v>22</v>
       </c>
       <c r="J73" s="2" t="s">
-        <v>151</v>
+        <v>32</v>
       </c>
       <c r="K73" s="2" t="s">
-        <v>24</v>
+        <v>39</v>
       </c>
       <c r="L73" s="2" t="s">
         <v>25</v>
@@ -4657,22 +4708,22 @@
     </row>
     <row r="74" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A74" s="2" t="s">
-        <v>200</v>
+        <v>215</v>
       </c>
       <c r="B74" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>153</v>
+        <v>163</v>
       </c>
       <c r="D74" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E74" s="2" t="s">
-        <v>201</v>
+        <v>216</v>
       </c>
       <c r="F74" s="2" t="s">
-        <v>201</v>
+        <v>216</v>
       </c>
       <c r="G74" s="2" t="s">
         <v>38</v>
@@ -4684,7 +4735,7 @@
         <v>22</v>
       </c>
       <c r="J74" s="2" t="s">
-        <v>151</v>
+        <v>32</v>
       </c>
       <c r="K74" s="2" t="s">
         <v>24</v>
@@ -4704,22 +4755,22 @@
     </row>
     <row r="75" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A75" s="2" t="s">
-        <v>166</v>
+        <v>217</v>
       </c>
       <c r="B75" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>153</v>
+        <v>163</v>
       </c>
       <c r="D75" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E75" s="2" t="s">
-        <v>202</v>
+        <v>218</v>
       </c>
       <c r="F75" s="2" t="s">
-        <v>202</v>
+        <v>218</v>
       </c>
       <c r="G75" s="2" t="s">
         <v>20</v>
@@ -4731,10 +4782,10 @@
         <v>22</v>
       </c>
       <c r="J75" s="2" t="s">
-        <v>151</v>
+        <v>32</v>
       </c>
       <c r="K75" s="2" t="s">
-        <v>24</v>
+        <v>77</v>
       </c>
       <c r="L75" s="2" t="s">
         <v>25</v>
@@ -4751,7 +4802,7 @@
     </row>
     <row r="76" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A76" s="2" t="s">
-        <v>138</v>
+        <v>219</v>
       </c>
       <c r="B76" s="2" t="s">
         <v>16</v>
@@ -4763,10 +4814,10 @@
         <v>18</v>
       </c>
       <c r="E76" s="2" t="s">
-        <v>203</v>
+        <v>220</v>
       </c>
       <c r="F76" s="2" t="s">
-        <v>203</v>
+        <v>220</v>
       </c>
       <c r="G76" s="2" t="s">
         <v>38</v>
@@ -4778,10 +4829,10 @@
         <v>22</v>
       </c>
       <c r="J76" s="2" t="s">
-        <v>151</v>
+        <v>32</v>
       </c>
       <c r="K76" s="2" t="s">
-        <v>24</v>
+        <v>60</v>
       </c>
       <c r="L76" s="2" t="s">
         <v>25</v>
@@ -4801,16 +4852,16 @@
         <v>66</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>16</v>
+        <v>41</v>
       </c>
       <c r="C77" s="2" t="s">
         <v>17</v>
       </c>
       <c r="D77" s="2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="E77" s="2" t="s">
-        <v>204</v>
+        <v>221</v>
       </c>
       <c r="F77" s="2" t="s">
         <v>68</v>
@@ -4819,16 +4870,16 @@
         <v>38</v>
       </c>
       <c r="H77" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="I77" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="J77" s="2" t="s">
-        <v>205</v>
+        <v>100</v>
       </c>
       <c r="K77" s="2" t="s">
-        <v>24</v>
+        <v>60</v>
       </c>
       <c r="L77" s="2" t="s">
         <v>25</v>
@@ -4837,30 +4888,30 @@
         <v>26</v>
       </c>
       <c r="N77" s="2" t="s">
-        <v>158</v>
+        <v>167</v>
       </c>
       <c r="O77" s="2" t="s">
-        <v>159</v>
+        <v>168</v>
       </c>
     </row>
     <row r="78" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A78" s="2" t="s">
-        <v>166</v>
+        <v>222</v>
       </c>
       <c r="B78" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>153</v>
+        <v>163</v>
       </c>
       <c r="D78" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E78" s="2" t="s">
-        <v>206</v>
+        <v>223</v>
       </c>
       <c r="F78" s="2" t="s">
-        <v>206</v>
+        <v>223</v>
       </c>
       <c r="G78" s="2" t="s">
         <v>20</v>
@@ -4872,10 +4923,10 @@
         <v>22</v>
       </c>
       <c r="J78" s="2" t="s">
-        <v>205</v>
+        <v>100</v>
       </c>
       <c r="K78" s="2" t="s">
-        <v>24</v>
+        <v>126</v>
       </c>
       <c r="L78" s="2" t="s">
         <v>25</v>
@@ -4884,15 +4935,15 @@
         <v>26</v>
       </c>
       <c r="N78" s="2" t="s">
-        <v>158</v>
+        <v>167</v>
       </c>
       <c r="O78" s="2" t="s">
-        <v>159</v>
+        <v>168</v>
       </c>
     </row>
     <row r="79" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A79" s="2" t="s">
-        <v>207</v>
+        <v>224</v>
       </c>
       <c r="B79" s="2" t="s">
         <v>16</v>
@@ -4904,10 +4955,10 @@
         <v>18</v>
       </c>
       <c r="E79" s="2" t="s">
-        <v>208</v>
+        <v>225</v>
       </c>
       <c r="F79" s="2" t="s">
-        <v>208</v>
+        <v>225</v>
       </c>
       <c r="G79" s="2" t="s">
         <v>38</v>
@@ -4919,10 +4970,10 @@
         <v>22</v>
       </c>
       <c r="J79" s="2" t="s">
-        <v>157</v>
+        <v>91</v>
       </c>
       <c r="K79" s="2" t="s">
-        <v>24</v>
+        <v>39</v>
       </c>
       <c r="L79" s="2" t="s">
         <v>25</v>
@@ -4931,15 +4982,15 @@
         <v>26</v>
       </c>
       <c r="N79" s="2" t="s">
-        <v>158</v>
+        <v>167</v>
       </c>
       <c r="O79" s="2" t="s">
-        <v>159</v>
+        <v>168</v>
       </c>
     </row>
     <row r="80" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A80" s="2" t="s">
-        <v>209</v>
+        <v>226</v>
       </c>
       <c r="B80" s="2" t="s">
         <v>16</v>
@@ -4951,10 +5002,10 @@
         <v>18</v>
       </c>
       <c r="E80" s="2" t="s">
-        <v>210</v>
+        <v>227</v>
       </c>
       <c r="F80" s="2" t="s">
-        <v>210</v>
+        <v>227</v>
       </c>
       <c r="G80" s="2" t="s">
         <v>38</v>
@@ -4966,10 +5017,10 @@
         <v>22</v>
       </c>
       <c r="J80" s="2" t="s">
-        <v>157</v>
+        <v>91</v>
       </c>
       <c r="K80" s="2" t="s">
-        <v>24</v>
+        <v>39</v>
       </c>
       <c r="L80" s="2" t="s">
         <v>25</v>
@@ -4978,15 +5029,15 @@
         <v>26</v>
       </c>
       <c r="N80" s="2" t="s">
-        <v>158</v>
+        <v>167</v>
       </c>
       <c r="O80" s="2" t="s">
-        <v>159</v>
+        <v>168</v>
       </c>
     </row>
     <row r="81" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A81" s="2" t="s">
-        <v>211</v>
+        <v>228</v>
       </c>
       <c r="B81" s="2" t="s">
         <v>16</v>
@@ -4998,10 +5049,10 @@
         <v>18</v>
       </c>
       <c r="E81" s="2" t="s">
-        <v>212</v>
+        <v>229</v>
       </c>
       <c r="F81" s="2" t="s">
-        <v>212</v>
+        <v>229</v>
       </c>
       <c r="G81" s="2" t="s">
         <v>38</v>
@@ -5013,10 +5064,10 @@
         <v>22</v>
       </c>
       <c r="J81" s="2" t="s">
-        <v>157</v>
+        <v>91</v>
       </c>
       <c r="K81" s="2" t="s">
-        <v>24</v>
+        <v>39</v>
       </c>
       <c r="L81" s="2" t="s">
         <v>25</v>
@@ -5025,15 +5076,15 @@
         <v>26</v>
       </c>
       <c r="N81" s="2" t="s">
-        <v>158</v>
+        <v>167</v>
       </c>
       <c r="O81" s="2" t="s">
-        <v>159</v>
+        <v>168</v>
       </c>
     </row>
     <row r="82" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A82" s="2" t="s">
-        <v>213</v>
+        <v>230</v>
       </c>
       <c r="B82" s="2" t="s">
         <v>16</v>
@@ -5045,10 +5096,10 @@
         <v>18</v>
       </c>
       <c r="E82" s="2" t="s">
-        <v>214</v>
+        <v>231</v>
       </c>
       <c r="F82" s="2" t="s">
-        <v>214</v>
+        <v>231</v>
       </c>
       <c r="G82" s="2" t="s">
         <v>38</v>
@@ -5060,10 +5111,10 @@
         <v>22</v>
       </c>
       <c r="J82" s="2" t="s">
-        <v>157</v>
+        <v>91</v>
       </c>
       <c r="K82" s="2" t="s">
-        <v>24</v>
+        <v>39</v>
       </c>
       <c r="L82" s="2" t="s">
         <v>25</v>
@@ -5072,15 +5123,15 @@
         <v>26</v>
       </c>
       <c r="N82" s="2" t="s">
-        <v>158</v>
+        <v>167</v>
       </c>
       <c r="O82" s="2" t="s">
-        <v>159</v>
+        <v>168</v>
       </c>
     </row>
     <row r="83" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A83" s="2" t="s">
-        <v>215</v>
+        <v>232</v>
       </c>
       <c r="B83" s="2" t="s">
         <v>16</v>
@@ -5092,10 +5143,10 @@
         <v>18</v>
       </c>
       <c r="E83" s="2" t="s">
-        <v>216</v>
+        <v>233</v>
       </c>
       <c r="F83" s="2" t="s">
-        <v>216</v>
+        <v>233</v>
       </c>
       <c r="G83" s="2" t="s">
         <v>20</v>
@@ -5107,10 +5158,10 @@
         <v>22</v>
       </c>
       <c r="J83" s="2" t="s">
-        <v>157</v>
+        <v>91</v>
       </c>
       <c r="K83" s="2" t="s">
-        <v>24</v>
+        <v>39</v>
       </c>
       <c r="L83" s="2" t="s">
         <v>25</v>
@@ -5119,15 +5170,15 @@
         <v>26</v>
       </c>
       <c r="N83" s="2" t="s">
-        <v>158</v>
+        <v>167</v>
       </c>
       <c r="O83" s="2" t="s">
-        <v>159</v>
+        <v>168</v>
       </c>
     </row>
     <row r="84" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A84" s="2" t="s">
-        <v>217</v>
+        <v>234</v>
       </c>
       <c r="B84" s="2" t="s">
         <v>16</v>
@@ -5139,10 +5190,10 @@
         <v>18</v>
       </c>
       <c r="E84" s="2" t="s">
-        <v>218</v>
+        <v>235</v>
       </c>
       <c r="F84" s="2" t="s">
-        <v>218</v>
+        <v>235</v>
       </c>
       <c r="G84" s="2" t="s">
         <v>38</v>
@@ -5154,10 +5205,10 @@
         <v>22</v>
       </c>
       <c r="J84" s="2" t="s">
-        <v>219</v>
+        <v>236</v>
       </c>
       <c r="K84" s="2" t="s">
-        <v>24</v>
+        <v>105</v>
       </c>
       <c r="L84" s="2" t="s">
         <v>25</v>
@@ -5166,62 +5217,62 @@
         <v>26</v>
       </c>
       <c r="N84" s="2" t="s">
-        <v>158</v>
+        <v>167</v>
       </c>
       <c r="O84" s="2" t="s">
-        <v>159</v>
+        <v>168</v>
       </c>
     </row>
     <row r="85" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A85" s="2" t="s">
-        <v>220</v>
+        <v>237</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>16</v>
+        <v>41</v>
       </c>
       <c r="C85" s="2" t="s">
         <v>17</v>
       </c>
       <c r="D85" s="2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="E85" s="2" t="s">
-        <v>221</v>
+        <v>238</v>
       </c>
       <c r="F85" s="2" t="s">
-        <v>222</v>
+        <v>239</v>
       </c>
       <c r="G85" s="2" t="s">
         <v>38</v>
       </c>
       <c r="H85" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="I85" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="J85" s="2" t="s">
-        <v>223</v>
+        <v>240</v>
       </c>
       <c r="K85" s="2" t="s">
-        <v>173</v>
+        <v>185</v>
       </c>
       <c r="L85" s="2" t="s">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="M85" s="2" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="N85" s="2" t="s">
         <v>34</v>
       </c>
       <c r="O85" s="2" t="s">
-        <v>159</v>
+        <v>168</v>
       </c>
     </row>
     <row r="86" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A86" s="2" t="s">
-        <v>224</v>
+        <v>241</v>
       </c>
       <c r="B86" s="2" t="s">
         <v>16</v>
@@ -5233,10 +5284,10 @@
         <v>18</v>
       </c>
       <c r="E86" s="2" t="s">
-        <v>225</v>
+        <v>242</v>
       </c>
       <c r="F86" s="2" t="s">
-        <v>225</v>
+        <v>242</v>
       </c>
       <c r="G86" s="2" t="s">
         <v>38</v>
@@ -5248,74 +5299,74 @@
         <v>22</v>
       </c>
       <c r="J86" s="2" t="s">
-        <v>223</v>
+        <v>240</v>
       </c>
       <c r="K86" s="2" t="s">
-        <v>24</v>
+        <v>39</v>
       </c>
       <c r="L86" s="2" t="s">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="M86" s="2" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="N86" s="2" t="s">
         <v>34</v>
       </c>
       <c r="O86" s="2" t="s">
-        <v>159</v>
+        <v>168</v>
       </c>
     </row>
     <row r="87" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A87" s="2" t="s">
-        <v>226</v>
+        <v>243</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>16</v>
+        <v>41</v>
       </c>
       <c r="C87" s="2" t="s">
         <v>17</v>
       </c>
       <c r="D87" s="2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="E87" s="2" t="s">
-        <v>227</v>
+        <v>244</v>
       </c>
       <c r="F87" s="2" t="s">
-        <v>228</v>
+        <v>245</v>
       </c>
       <c r="G87" s="2" t="s">
         <v>38</v>
       </c>
       <c r="H87" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="I87" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="J87" s="2" t="s">
-        <v>223</v>
+        <v>240</v>
       </c>
       <c r="K87" s="2" t="s">
-        <v>173</v>
+        <v>185</v>
       </c>
       <c r="L87" s="2" t="s">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="M87" s="2" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="N87" s="2" t="s">
         <v>34</v>
       </c>
       <c r="O87" s="2" t="s">
-        <v>159</v>
+        <v>168</v>
       </c>
     </row>
     <row r="88" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A88" s="2" t="s">
-        <v>229</v>
+        <v>246</v>
       </c>
       <c r="B88" s="2" t="s">
         <v>16</v>
@@ -5327,10 +5378,10 @@
         <v>18</v>
       </c>
       <c r="E88" s="2" t="s">
-        <v>230</v>
+        <v>247</v>
       </c>
       <c r="F88" s="2" t="s">
-        <v>230</v>
+        <v>247</v>
       </c>
       <c r="G88" s="2" t="s">
         <v>38</v>
@@ -5342,22 +5393,22 @@
         <v>22</v>
       </c>
       <c r="J88" s="2" t="s">
-        <v>223</v>
+        <v>240</v>
       </c>
       <c r="K88" s="2" t="s">
-        <v>24</v>
+        <v>39</v>
       </c>
       <c r="L88" s="2" t="s">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="M88" s="2" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="N88" s="2" t="s">
         <v>34</v>
       </c>
       <c r="O88" s="2" t="s">
-        <v>159</v>
+        <v>168</v>
       </c>
     </row>
   </sheetData>
@@ -5373,23 +5424,23 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>231</v>
+        <v>248</v>
       </c>
       <c r="B1" s="3"/>
       <c r="C1" s="3"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>232</v>
+        <v>249</v>
       </c>
       <c r="B2" t="s">
-        <v>233</v>
+        <v>250</v>
       </c>
       <c r="D2" t="s">
-        <v>234</v>
+        <v>251</v>
       </c>
       <c r="E2" t="s">
-        <v>235</v>
+        <v>252</v>
       </c>
       <c r="F2"/>
       <c r="G2"/>
@@ -5397,16 +5448,16 @@
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>236</v>
+        <v>253</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>237</v>
+        <v>254</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>238</v>
+        <v>255</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>239</v>
+        <v>256</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
@@ -5417,15 +5468,15 @@
         <v>0</v>
       </c>
       <c r="G5" s="4">
-        <v>315.67</v>
+        <v>21.93</v>
       </c>
       <c r="J5" s="4">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="21" spans="10:10" x14ac:dyDescent="0.25">
       <c r="J21" s="6" t="s">
-        <v>240</v>
+        <v>257</v>
       </c>
     </row>
     <row r="22" spans="10:11" x14ac:dyDescent="0.25">
@@ -5438,7 +5489,7 @@
     </row>
     <row r="23" spans="10:11" x14ac:dyDescent="0.25">
       <c r="J23" t="s">
-        <v>241</v>
+        <v>258</v>
       </c>
       <c r="K23">
         <v>0</v>
@@ -5446,7 +5497,7 @@
     </row>
     <row r="24" spans="10:11" x14ac:dyDescent="0.25">
       <c r="J24" t="s">
-        <v>242</v>
+        <v>259</v>
       </c>
       <c r="K24">
         <v>0</v>
@@ -5477,12 +5528,12 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
-        <v>243</v>
+        <v>260</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>236</v>
+        <v>253</v>
       </c>
       <c r="B2">
         <v>87</v>
@@ -5496,35 +5547,35 @@
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6">
-        <v>315.67</v>
+        <v>21.93</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
-        <v>244</v>
+        <v>261</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>245</v>
+        <v>262</v>
       </c>
       <c r="G9" s="6" t="s">
         <v>6</v>
       </c>
       <c r="J9" s="6" t="s">
-        <v>246</v>
+        <v>263</v>
       </c>
       <c r="M9" s="6" t="s">
-        <v>247</v>
+        <v>264</v>
       </c>
       <c r="P9" s="6" t="s">
-        <v>248</v>
+        <v>265</v>
       </c>
       <c r="Q9" s="6" t="s">
-        <v>249</v>
+        <v>266</v>
       </c>
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.25">
@@ -5532,7 +5583,7 @@
         <v>16</v>
       </c>
       <c r="B10">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="D10" t="s">
         <v>17</v>
@@ -5541,13 +5592,13 @@
         <v>67</v>
       </c>
       <c r="G10" t="s">
-        <v>250</v>
+        <v>267</v>
       </c>
       <c r="H10">
         <v>0</v>
       </c>
       <c r="J10" t="s">
-        <v>251</v>
+        <v>268</v>
       </c>
       <c r="K10">
         <v>0</v>
@@ -5559,15 +5610,21 @@
         <v>71</v>
       </c>
       <c r="P10" t="s">
-        <v>158</v>
+        <v>167</v>
       </c>
       <c r="Q10">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="11" spans="4:17" x14ac:dyDescent="0.25">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>41</v>
+      </c>
+      <c r="B11">
+        <v>6</v>
+      </c>
       <c r="D11" t="s">
-        <v>153</v>
+        <v>163</v>
       </c>
       <c r="E11">
         <v>12</v>
@@ -5582,10 +5639,10 @@
         <v>26</v>
       </c>
       <c r="K11">
-        <v>71</v>
+        <v>87</v>
       </c>
       <c r="M11" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="N11">
         <v>6</v>
@@ -5594,10 +5651,16 @@
         <v>34</v>
       </c>
       <c r="Q11">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="12" spans="4:17" x14ac:dyDescent="0.25">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>180</v>
+      </c>
+      <c r="B12">
+        <v>1</v>
+      </c>
       <c r="D12" t="s">
         <v>75</v>
       </c>
@@ -5611,73 +5674,67 @@
         <v>70</v>
       </c>
       <c r="J12" t="s">
-        <v>252</v>
+        <v>269</v>
       </c>
       <c r="K12">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="M12" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="N12">
         <v>2</v>
       </c>
       <c r="P12" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="Q12">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D13" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="E13">
         <v>3</v>
       </c>
       <c r="G13" t="s">
-        <v>253</v>
+        <v>270</v>
       </c>
       <c r="H13">
         <v>0</v>
       </c>
       <c r="M13" t="s">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="N13">
         <v>7</v>
       </c>
       <c r="P13" t="s">
-        <v>70</v>
+        <v>27</v>
       </c>
       <c r="Q13">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="14" spans="7:17" x14ac:dyDescent="0.25">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="14" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G14" t="s">
-        <v>254</v>
+        <v>271</v>
       </c>
       <c r="H14">
         <v>0</v>
       </c>
       <c r="M14" t="s">
-        <v>241</v>
+        <v>258</v>
       </c>
       <c r="N14">
         <v>0</v>
       </c>
-      <c r="P14" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q14">
-        <v>20</v>
-      </c>
     </row>
     <row r="15" spans="13:14" x14ac:dyDescent="0.25">
       <c r="M15" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="N15">
         <v>1</v>
@@ -5685,7 +5742,7 @@
     </row>
     <row r="16" spans="13:14" x14ac:dyDescent="0.25">
       <c r="M16" t="s">
-        <v>255</v>
+        <v>272</v>
       </c>
       <c r="N16">
         <v>0</v>
@@ -5693,7 +5750,7 @@
     </row>
     <row r="17" spans="13:14" x14ac:dyDescent="0.25">
       <c r="M17" t="s">
-        <v>256</v>
+        <v>273</v>
       </c>
       <c r="N17">
         <v>0</v>
@@ -5701,10 +5758,10 @@
     </row>
     <row r="19" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D19" s="6" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="20" ht="18" customHeight="1" spans="4:7" x14ac:dyDescent="0.25">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="20" spans="4:7" x14ac:dyDescent="0.25">
       <c r="D20" s="1" t="s">
         <v>0</v>
       </c>
@@ -5712,7 +5769,7 @@
         <v>1</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>258</v>
+        <v>275</v>
       </c>
       <c r="G20" s="1" t="s">
         <v>4</v>
@@ -5720,142 +5777,142 @@
     </row>
     <row r="21" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D21" s="2" t="s">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F21" s="2">
-        <v>339</v>
+        <v>383</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>41</v>
+        <v>30</v>
       </c>
     </row>
     <row r="22" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D22" s="2" t="s">
-        <v>169</v>
+        <v>55</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F22" s="2">
-        <v>309</v>
+        <v>383</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>170</v>
+        <v>56</v>
       </c>
     </row>
     <row r="23" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D23" s="2" t="s">
-        <v>50</v>
+        <v>131</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F23" s="2">
-        <v>254</v>
+        <v>383</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>51</v>
+        <v>132</v>
       </c>
     </row>
     <row r="24" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D24" s="2" t="s">
-        <v>15</v>
+        <v>136</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F24" s="2">
-        <v>0</v>
+        <v>383</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>19</v>
+        <v>137</v>
       </c>
     </row>
     <row r="25" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D25" s="2" t="s">
-        <v>36</v>
+        <v>142</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F25" s="2">
-        <v>0</v>
+        <v>383</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>37</v>
+        <v>143</v>
       </c>
     </row>
     <row r="26" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D26" s="2" t="s">
-        <v>46</v>
+        <v>160</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F26" s="2">
-        <v>0</v>
+        <v>383</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>47</v>
+        <v>161</v>
       </c>
     </row>
     <row r="27" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D27" s="2" t="s">
-        <v>59</v>
+        <v>165</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F27" s="2">
-        <v>0</v>
+        <v>383</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>60</v>
+        <v>166</v>
       </c>
     </row>
     <row r="28" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D28" s="2" t="s">
-        <v>61</v>
+        <v>188</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F28" s="2">
-        <v>0</v>
+        <v>383</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>62</v>
+        <v>189</v>
       </c>
     </row>
     <row r="29" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D29" s="2" t="s">
-        <v>64</v>
+        <v>192</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F29" s="2">
-        <v>0</v>
+        <v>383</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>65</v>
+        <v>193</v>
       </c>
     </row>
     <row r="30" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D30" s="2" t="s">
-        <v>66</v>
+        <v>198</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F30" s="2">
-        <v>0</v>
+        <v>383</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>67</v>
+        <v>199</v>
       </c>
     </row>
   </sheetData>
